--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D79386-81A4-42DB-BB07-FEC086A572D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F62E682-C746-4917-8339-5612AA86346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="601">
   <si>
     <t>Time</t>
   </si>
@@ -1634,172 +1634,190 @@
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b29-6792-5ba3-a1fe-059df342f346</t>
   </si>
   <si>
-    <t>12/25/2025 6:38:04 PM</t>
-  </si>
-  <si>
     <t>7052 Houston</t>
   </si>
   <si>
     <t>Construction, Light Traffic, Night</t>
   </si>
   <si>
-    <t>Jacob T Scully</t>
-  </si>
-  <si>
-    <t>Julius Schepps Freeway, 5.8 mi ESE Lancaster, Dallas County, TX, 76125</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455817-5ced-5831-9e6c-927cf4706648</t>
-  </si>
-  <si>
-    <t>12/25/2025 11:55:00 AM</t>
-  </si>
-  <si>
-    <t>Hardy Toll Road, 2.8 mi N Aldine, Harris County, TX, 77073</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544556a6-585c-502b-bbc3-77893c2a581a</t>
-  </si>
-  <si>
-    <t>12/24/2025 10:13:52 AM</t>
-  </si>
-  <si>
-    <t>9045 Liberty Road, Houston, TX, 77028</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455123-622a-5c65-a7f0-400ffc8d0d1b</t>
-  </si>
-  <si>
-    <t>12/23/2025 5:17:52 PM</t>
-  </si>
-  <si>
-    <t>18124 Gulf Freeway, Houston, TX, 77546</t>
-  </si>
-  <si>
     <t>37</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454d81-3818-5d17-baba-c88e2a976802</t>
-  </si>
-  <si>
-    <t>12/23/2025 4:10:18 PM</t>
-  </si>
-  <si>
-    <t>6462 San Diego</t>
-  </si>
-  <si>
-    <t>Manuel Simental</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Cyclist/Motorcyclist, Light Traffic</t>
-  </si>
-  <si>
-    <t>9177 Airway Road, San Diego, CA, 92154</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454d43-5b63-5f1a-8f84-39bea477fc3c</t>
-  </si>
-  <si>
-    <t>12/23/2025 1:23:57 PM</t>
-  </si>
-  <si>
-    <t>8227 Gulf Freeway, Houston, TX, 77017</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454cab-1089-5aeb-8398-90db5d568cc6</t>
-  </si>
-  <si>
-    <t>12/23/2025 1:22:22 PM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway, Houston, TX, 77093</t>
-  </si>
-  <si>
     <t>51</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454ca9-9ced-5d40-ac6c-55b20aabc95b</t>
-  </si>
-  <si>
-    <t>12/23/2025 12:32:18 PM</t>
-  </si>
-  <si>
-    <t>4688 San Diego</t>
-  </si>
-  <si>
-    <t>HAAS Alert, San Diego, CA, Service Trucks</t>
-  </si>
-  <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>8701 Siempre Viva Road, San Diego, CA, 92154</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454c7b-c5c5-5e03-ab17-7bf58a1eb2c5</t>
-  </si>
-  <si>
-    <t>12/23/2025 9:40:42 AM</t>
-  </si>
-  <si>
-    <t>I 2;US 83, Mercedes, TX, 78570</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454bde-a973-5148-8108-b28c81c6b8f1</t>
-  </si>
-  <si>
-    <t>12/23/2025 8:46:37 AM</t>
-  </si>
-  <si>
-    <t>Almeda Road, Houston, TX, 77045</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454bad-2710-5d41-9f33-b616ae80794d</t>
-  </si>
-  <si>
-    <t>12/22/2025 10:20:25 PM</t>
-  </si>
-  <si>
-    <t>Cross Colony Drive, League City, TX, 77539-9332</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445496f-dafa-5fe1-8b7b-1927641633e2</t>
-  </si>
-  <si>
-    <t>12/22/2025 2:34:09 PM</t>
-  </si>
-  <si>
-    <t>0654 Houston</t>
-  </si>
-  <si>
-    <t>Construction, Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>9498 Alameda Avenue, El Paso, TX, 79907</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544547c4-f616-5696-bbc1-9d876dca9f5e</t>
-  </si>
-  <si>
-    <t>12/22/2025 7:35:55 AM</t>
-  </si>
-  <si>
-    <t>South Loop East, Houston, TX, 77033</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454646-1249-5d6f-961d-957ca3230fd6</t>
-  </si>
-  <si>
-    <t>12/21/2025 3:55:50 PM</t>
-  </si>
-  <si>
-    <t>Cullen Boulevard, Houston, TX, 77021</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544542e9-65b0-5481-ae2e-f839eb34d5c1</t>
+    <t>03/26/2026 4:34:48 PM</t>
+  </si>
+  <si>
+    <t>East Vinton Road, Westway Number 2 Colonia, TX, 79821</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c12-4532-598e-9540-8d2ff9064c99</t>
+  </si>
+  <si>
+    <t>03/26/2026 12:27:51 PM</t>
+  </si>
+  <si>
+    <t>I 2;US 83, Alamo, TX, 78516</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b30-2e3b-562e-9623-00fd5f5aaa37</t>
+  </si>
+  <si>
+    <t>03/25/2026 1:58:02 PM</t>
+  </si>
+  <si>
+    <t>7056 Houston</t>
+  </si>
+  <si>
+    <t>12308 Fuqua Street, Houston, TX, 77034</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445265c-62f0-5a30-9f78-0e965473426d</t>
+  </si>
+  <si>
+    <t>03/25/2026 4:27:58 AM</t>
+  </si>
+  <si>
+    <t>RudyRodriguez</t>
+  </si>
+  <si>
+    <t>Northwest Freeway, Houston, TX, 77092-7005</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452452-79b5-5b86-ab7a-7d2cf1ede108</t>
+  </si>
+  <si>
+    <t>03/24/2026 5:36:25 PM</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544521fd-f93c-5cfc-bf4b-eda4db3200bd</t>
+  </si>
+  <si>
+    <t>03/24/2026 12:18:03 PM</t>
+  </si>
+  <si>
+    <t>Southwest Freeway Frontage Road, Houston, TX, 77046</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544520da-7f25-55fe-8055-cbfe201979e7</t>
+  </si>
+  <si>
+    <t>03/23/2026 4:21:48 PM</t>
+  </si>
+  <si>
+    <t>East Loop North, Houston, TX, 77029</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c93-4b3c-5ae0-96d1-31d6e9c7b502</t>
+  </si>
+  <si>
+    <t>03/23/2026 3:18:41 PM</t>
+  </si>
+  <si>
+    <t>8361 Tucson</t>
+  </si>
+  <si>
+    <t>Guy Henderson</t>
+  </si>
+  <si>
+    <t>Nogales, AZ, Tucson, AZ, Yuma, AZ</t>
+  </si>
+  <si>
+    <t>Guy N Henderson - Tucson</t>
+  </si>
+  <si>
+    <t>South Kings Highway, 5.1 mi W Douglas, Cochise County, AZ, 85626</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c59-81c0-5847-99f6-c62a9f458e43</t>
+  </si>
+  <si>
+    <t>03/23/2026 9:48:17 AM</t>
+  </si>
+  <si>
+    <t>5438 El Paso</t>
+  </si>
+  <si>
+    <t>Northwest Freeway Frontage Road, Jersey Village, TX, 77065:77429</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451b2b-04df-590c-a501-10db316e8507</t>
+  </si>
+  <si>
+    <t>03/22/2026 3:30:41 AM</t>
+  </si>
+  <si>
+    <t>North Loop West, Houston, TX, 77008</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544514aa-f384-571b-bb40-c7e71c4e5e98</t>
+  </si>
+  <si>
+    <t>03/21/2026 3:12:04 PM</t>
+  </si>
+  <si>
+    <t>North Freeway, Houston, TX, 77037</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451206-bb58-5166-ab43-97b58c8dac3d</t>
+  </si>
+  <si>
+    <t>03/20/2026 2:10:51 PM</t>
+  </si>
+  <si>
+    <t>Todd Johnston</t>
+  </si>
+  <si>
+    <t>I 35;US 77, Bellmead, TX, 76705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450ca8-53ba-58de-b474-e36e7dfe067f</t>
+  </si>
+  <si>
+    <t>03/20/2026 11:11:41 AM</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Construction, Pedestrians, Light Traffic</t>
+  </si>
+  <si>
+    <t>2755 Clinton Drive, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450c04-4b4f-5269-9e3d-ecded278ae39</t>
+  </si>
+  <si>
+    <t>03/20/2026 10:30:12 AM</t>
+  </si>
+  <si>
+    <t>El Cibolo Road, Faysville, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450bde-4fc5-5ad7-b1ad-b3af4a64bdc4</t>
+  </si>
+  <si>
+    <t>03/20/2026 7:11:29 AM</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>4957 Hull Street, Houston, TX, 77021</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b28-624c-5700-8145-29c59b89af40</t>
   </si>
 </sst>
 </file>
@@ -2176,10 +2194,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O126"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:O127"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2226,133 +2244,133 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>544</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>545</v>
+      </c>
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>546</v>
+      </c>
+      <c r="O2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>549</v>
+      </c>
+      <c r="K3" t="s">
+        <v>550</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
       <c r="I4" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>554</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -2364,30 +2382,30 @@
         <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.75">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>556</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>557</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>354</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -2396,10 +2414,10 @@
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>558</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>537</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
@@ -2411,18 +2429,18 @@
         <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.75">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>560</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>539</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
         <v>30</v>
@@ -2431,48 +2449,48 @@
         <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
         <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>400</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>561</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N6" t="s">
         <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.75">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>563</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -2481,19 +2499,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>564</v>
       </c>
       <c r="K7" t="s">
-        <v>64</v>
+        <v>281</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -2505,18 +2523,18 @@
         <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.75">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>566</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -2525,10 +2543,10 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -2537,57 +2555,57 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>67</v>
+        <v>567</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
         <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.75">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>569</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>570</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>572</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>467</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>543</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>573</v>
       </c>
       <c r="J9" t="s">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
@@ -2596,30 +2614,30 @@
         <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.75">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>576</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>577</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
         <v>33</v>
@@ -2631,105 +2649,105 @@
         <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="K10" t="s">
+        <v>281</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" t="s">
+        <v>540</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>581</v>
+      </c>
+      <c r="K11" t="s">
+        <v>542</v>
+      </c>
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>583</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>584</v>
+      </c>
+      <c r="K12" t="s">
         <v>84</v>
       </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" t="s">
-        <v>98</v>
-      </c>
-      <c r="K12" t="s">
-        <v>99</v>
-      </c>
       <c r="L12" t="s">
         <v>23</v>
       </c>
@@ -2740,65 +2758,65 @@
         <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.75">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>586</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>539</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>587</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
         <v>33</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>588</v>
       </c>
       <c r="K13" t="s">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L13" t="s">
         <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N13" t="s">
         <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.75">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>590</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
         <v>30</v>
@@ -2807,22 +2825,22 @@
         <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>107</v>
+        <v>592</v>
       </c>
       <c r="K14" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s">
         <v>23</v>
@@ -2834,30 +2852,30 @@
         <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.75">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>594</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>454</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2866,10 +2884,10 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>112</v>
+        <v>595</v>
       </c>
       <c r="K15" t="s">
-        <v>113</v>
+        <v>401</v>
       </c>
       <c r="L15" t="s">
         <v>23</v>
@@ -2881,18 +2899,18 @@
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.75">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>597</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>397</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>398</v>
       </c>
       <c r="D16" t="s">
         <v>30</v>
@@ -2904,7 +2922,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>598</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -2913,10 +2931,10 @@
         <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>116</v>
+        <v>599</v>
       </c>
       <c r="K16" t="s">
-        <v>117</v>
+        <v>541</v>
       </c>
       <c r="L16" t="s">
         <v>23</v>
@@ -2928,42 +2946,42 @@
         <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.75">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
         <v>23</v>
@@ -2975,42 +2993,42 @@
         <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>33</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="K18" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
         <v>23</v>
@@ -3022,18 +3040,18 @@
         <v>23</v>
       </c>
       <c r="O18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.75">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
@@ -3042,148 +3060,148 @@
         <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
         <v>42</v>
       </c>
       <c r="H19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K19" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" t="s">
         <v>22</v>
       </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" t="s">
-        <v>133</v>
-      </c>
-      <c r="K19" t="s">
-        <v>134</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" t="s">
-        <v>135</v>
-      </c>
-      <c r="O19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
         <v>20</v>
       </c>
-      <c r="G20" t="s">
-        <v>138</v>
-      </c>
-      <c r="H20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" t="s">
-        <v>139</v>
-      </c>
-      <c r="K20" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" t="s">
-        <v>23</v>
-      </c>
-      <c r="N20" t="s">
-        <v>23</v>
-      </c>
-      <c r="O20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="G21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" t="s">
-        <v>144</v>
-      </c>
-      <c r="G21" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" t="s">
-        <v>146</v>
-      </c>
-      <c r="K21" t="s">
-        <v>147</v>
-      </c>
-      <c r="L21" t="s">
-        <v>23</v>
-      </c>
-      <c r="M21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" t="s">
-        <v>150</v>
-      </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
         <v>33</v>
@@ -3195,10 +3213,10 @@
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>155</v>
+        <v>63</v>
       </c>
       <c r="K22" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="L22" t="s">
         <v>23</v>
@@ -3210,15 +3228,15 @@
         <v>23</v>
       </c>
       <c r="O22" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.75">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>62</v>
@@ -3230,22 +3248,22 @@
         <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="K23" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="L23" t="s">
         <v>23</v>
@@ -3254,21 +3272,21 @@
         <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
         <v>30</v>
@@ -3277,7 +3295,7 @@
         <v>31</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s">
         <v>33</v>
@@ -3289,10 +3307,10 @@
         <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="K24" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="L24" t="s">
         <v>23</v>
@@ -3301,33 +3319,33 @@
         <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="O24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.75">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
         <v>82</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
@@ -3336,7 +3354,7 @@
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s">
         <v>84</v>
@@ -3351,30 +3369,30 @@
         <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.75">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s">
         <v>34</v>
@@ -3383,10 +3401,10 @@
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="L26" t="s">
         <v>23</v>
@@ -3395,45 +3413,45 @@
         <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.75">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="K27" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s">
         <v>23</v>
@@ -3445,89 +3463,89 @@
         <v>23</v>
       </c>
       <c r="O27" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I28" t="s">
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s">
         <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N28" t="s">
         <v>23</v>
       </c>
       <c r="O28" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.75">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I29" t="s">
         <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="K29" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s">
         <v>23</v>
@@ -3539,42 +3557,42 @@
         <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.75">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
         <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="K30" t="s">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s">
         <v>23</v>
@@ -3586,66 +3604,66 @@
         <v>23</v>
       </c>
       <c r="O30" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.75">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
+        <v>116</v>
+      </c>
+      <c r="K31" t="s">
+        <v>117</v>
+      </c>
+      <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
         <v>56</v>
       </c>
-      <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" t="s">
-        <v>203</v>
-      </c>
-      <c r="H31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
-        <v>204</v>
-      </c>
-      <c r="K31" t="s">
-        <v>205</v>
-      </c>
-      <c r="L31" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" t="s">
-        <v>23</v>
-      </c>
-      <c r="N31" t="s">
-        <v>206</v>
-      </c>
-      <c r="O31" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A32" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
       <c r="D32" t="s">
         <v>30</v>
       </c>
@@ -3653,10 +3671,10 @@
         <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="H32" t="s">
         <v>34</v>
@@ -3665,10 +3683,10 @@
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="K32" t="s">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="L32" t="s">
         <v>23</v>
@@ -3677,30 +3695,30 @@
         <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>212</v>
+        <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.75">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
@@ -3712,10 +3730,10 @@
         <v>23</v>
       </c>
       <c r="J33" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="K33" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="L33" t="s">
         <v>23</v>
@@ -3727,18 +3745,18 @@
         <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.75">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
         <v>30</v>
@@ -3747,10 +3765,10 @@
         <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -3759,10 +3777,10 @@
         <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>221</v>
+        <v>133</v>
       </c>
       <c r="K34" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s">
         <v>23</v>
@@ -3771,21 +3789,21 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="O34" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.75">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
         <v>30</v>
@@ -3797,7 +3815,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="H35" t="s">
         <v>34</v>
@@ -3806,10 +3824,10 @@
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>225</v>
+        <v>139</v>
       </c>
       <c r="K35" t="s">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s">
         <v>23</v>
@@ -3821,18 +3839,18 @@
         <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.75">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
         <v>30</v>
@@ -3841,10 +3859,10 @@
         <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="H36" t="s">
         <v>34</v>
@@ -3853,10 +3871,10 @@
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="K36" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="L36" t="s">
         <v>23</v>
@@ -3868,42 +3886,42 @@
         <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.75">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="E37" t="s">
-        <v>234</v>
+        <v>153</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="G37" t="s">
         <v>33</v>
       </c>
       <c r="H37" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I37" t="s">
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="K37" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s">
         <v>23</v>
@@ -3915,512 +3933,512 @@
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.75">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="B38" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>158</v>
+      </c>
+      <c r="G38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
+        <v>159</v>
+      </c>
+      <c r="K38" t="s">
+        <v>160</v>
+      </c>
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" t="s">
+        <v>161</v>
+      </c>
+      <c r="O38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
+        <v>164</v>
+      </c>
+      <c r="K39" t="s">
+        <v>165</v>
+      </c>
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" t="s">
         <v>106</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>168</v>
       </c>
-      <c r="D38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" t="s">
-        <v>238</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
+        <v>170</v>
+      </c>
+      <c r="K40" t="s">
+        <v>84</v>
+      </c>
+      <c r="L40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>85</v>
+      </c>
+      <c r="N40" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" t="s">
+        <v>173</v>
+      </c>
+      <c r="G41" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" t="s">
+        <v>34</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
+        <v>174</v>
+      </c>
+      <c r="K41" t="s">
+        <v>175</v>
+      </c>
+      <c r="L41" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" t="s">
+        <v>176</v>
+      </c>
+      <c r="O41" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" t="s">
+        <v>183</v>
+      </c>
+      <c r="H42" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
+        <v>184</v>
+      </c>
+      <c r="K42" t="s">
+        <v>185</v>
+      </c>
+      <c r="L42" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" t="s">
+        <v>188</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" t="s">
+        <v>189</v>
+      </c>
+      <c r="K43" t="s">
+        <v>190</v>
+      </c>
+      <c r="L43" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" t="s">
+        <v>85</v>
+      </c>
+      <c r="N43" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" t="s">
         <v>42</v>
       </c>
-      <c r="H38" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" t="s">
-        <v>239</v>
-      </c>
-      <c r="K38" t="s">
-        <v>85</v>
-      </c>
-      <c r="L38" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" t="s">
-        <v>23</v>
-      </c>
-      <c r="O38" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A39" t="s">
-        <v>241</v>
-      </c>
-      <c r="B39" t="s">
-        <v>232</v>
-      </c>
-      <c r="C39" t="s">
-        <v>233</v>
-      </c>
-      <c r="D39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" t="s">
-        <v>234</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" t="s">
-        <v>242</v>
-      </c>
-      <c r="H39" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" t="s">
-        <v>243</v>
-      </c>
-      <c r="K39" t="s">
-        <v>84</v>
-      </c>
-      <c r="L39" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A40" t="s">
-        <v>245</v>
-      </c>
-      <c r="B40" t="s">
-        <v>246</v>
-      </c>
-      <c r="C40" t="s">
-        <v>247</v>
-      </c>
-      <c r="D40" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" t="s">
-        <v>248</v>
-      </c>
-      <c r="H40" t="s">
-        <v>34</v>
-      </c>
-      <c r="I40" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" t="s">
-        <v>249</v>
-      </c>
-      <c r="K40" t="s">
-        <v>165</v>
-      </c>
-      <c r="L40" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N40" t="s">
-        <v>250</v>
-      </c>
-      <c r="O40" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A41" t="s">
-        <v>252</v>
-      </c>
-      <c r="B41" t="s">
-        <v>253</v>
-      </c>
-      <c r="C41" t="s">
-        <v>254</v>
-      </c>
-      <c r="D41" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" t="s">
-        <v>255</v>
-      </c>
-      <c r="K41" t="s">
-        <v>165</v>
-      </c>
-      <c r="L41" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A42" t="s">
-        <v>257</v>
-      </c>
-      <c r="B42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
+        <v>193</v>
+      </c>
+      <c r="K44" t="s">
+        <v>194</v>
+      </c>
+      <c r="L44" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>199</v>
+      </c>
+      <c r="K45" t="s">
+        <v>200</v>
+      </c>
+      <c r="L45" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>202</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" t="s">
+        <v>203</v>
+      </c>
+      <c r="H46" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>204</v>
+      </c>
+      <c r="K46" t="s">
+        <v>205</v>
+      </c>
+      <c r="L46" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" t="s">
+        <v>206</v>
+      </c>
+      <c r="O46" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
+        <v>210</v>
+      </c>
+      <c r="K47" t="s">
+        <v>211</v>
+      </c>
+      <c r="L47" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" t="s">
+        <v>212</v>
+      </c>
+      <c r="O47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G48" t="s">
         <v>33</v>
       </c>
-      <c r="H42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" t="s">
-        <v>258</v>
-      </c>
-      <c r="K42" t="s">
-        <v>147</v>
-      </c>
-      <c r="L42" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" t="s">
-        <v>85</v>
-      </c>
-      <c r="N42" t="s">
-        <v>23</v>
-      </c>
-      <c r="O42" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A43" t="s">
-        <v>260</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" t="s">
-        <v>33</v>
-      </c>
-      <c r="H43" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" t="s">
-        <v>261</v>
-      </c>
-      <c r="K43" t="s">
-        <v>84</v>
-      </c>
-      <c r="L43" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A44" t="s">
-        <v>263</v>
-      </c>
-      <c r="B44" t="s">
-        <v>246</v>
-      </c>
-      <c r="C44" t="s">
-        <v>247</v>
-      </c>
-      <c r="D44" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" t="s">
-        <v>73</v>
-      </c>
-      <c r="G44" t="s">
-        <v>264</v>
-      </c>
-      <c r="H44" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
-        <v>265</v>
-      </c>
-      <c r="K44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L44" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" t="s">
-        <v>23</v>
-      </c>
-      <c r="N44" t="s">
-        <v>206</v>
-      </c>
-      <c r="O44" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A45" t="s">
-        <v>267</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" t="s">
-        <v>50</v>
-      </c>
-      <c r="F45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" t="s">
-        <v>33</v>
-      </c>
-      <c r="H45" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" t="s">
-        <v>268</v>
-      </c>
-      <c r="J45" t="s">
-        <v>269</v>
-      </c>
-      <c r="K45" t="s">
-        <v>270</v>
-      </c>
-      <c r="L45" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" t="s">
-        <v>23</v>
-      </c>
-      <c r="N45" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A46" t="s">
-        <v>272</v>
-      </c>
-      <c r="B46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" t="s">
-        <v>33</v>
-      </c>
-      <c r="H46" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>273</v>
-      </c>
-      <c r="K46" t="s">
-        <v>274</v>
-      </c>
-      <c r="L46" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" t="s">
-        <v>23</v>
-      </c>
-      <c r="N46" t="s">
-        <v>23</v>
-      </c>
-      <c r="O46" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A47" t="s">
-        <v>276</v>
-      </c>
-      <c r="B47" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" t="s">
-        <v>152</v>
-      </c>
-      <c r="E47" t="s">
-        <v>153</v>
-      </c>
-      <c r="F47" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" t="s">
-        <v>33</v>
-      </c>
-      <c r="H47" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" t="s">
-        <v>277</v>
-      </c>
-      <c r="K47" t="s">
-        <v>122</v>
-      </c>
-      <c r="L47" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" t="s">
-        <v>23</v>
-      </c>
-      <c r="O47" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A48" t="s">
-        <v>279</v>
-      </c>
-      <c r="B48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" t="s">
-        <v>30</v>
-      </c>
-      <c r="E48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" t="s">
-        <v>42</v>
-      </c>
       <c r="H48" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I48" t="s">
         <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="K48" t="s">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="L48" t="s">
         <v>23</v>
@@ -4432,30 +4450,30 @@
         <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.75">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>215</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>32</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
@@ -4464,10 +4482,10 @@
         <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="L49" t="s">
         <v>23</v>
@@ -4479,27 +4497,27 @@
         <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.75">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>197</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
         <v>33</v>
@@ -4511,33 +4529,33 @@
         <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="K50" t="s">
-        <v>287</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s">
         <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N50" t="s">
         <v>23</v>
       </c>
       <c r="O50" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.75">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
         <v>30</v>
@@ -4546,10 +4564,10 @@
         <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="H51" t="s">
         <v>34</v>
@@ -4558,10 +4576,10 @@
         <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="K51" t="s">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="L51" t="s">
         <v>23</v>
@@ -4573,24 +4591,24 @@
         <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.75">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="C52" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
         <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="F52" t="s">
         <v>20</v>
@@ -4605,10 +4623,10 @@
         <v>23</v>
       </c>
       <c r="J52" t="s">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="K52" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L52" t="s">
         <v>23</v>
@@ -4620,18 +4638,18 @@
         <v>23</v>
       </c>
       <c r="O52" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.75">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s">
-        <v>246</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
         <v>30</v>
@@ -4640,69 +4658,69 @@
         <v>31</v>
       </c>
       <c r="F53" t="s">
+        <v>238</v>
+      </c>
+      <c r="G53" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" t="s">
+        <v>239</v>
+      </c>
+      <c r="K53" t="s">
+        <v>85</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" t="s">
+        <v>23</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>234</v>
+      </c>
+      <c r="F54" t="s">
         <v>20</v>
-      </c>
-      <c r="G53" t="s">
-        <v>297</v>
-      </c>
-      <c r="H53" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" t="s">
-        <v>298</v>
-      </c>
-      <c r="K53" t="s">
-        <v>299</v>
-      </c>
-      <c r="L53" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" t="s">
-        <v>23</v>
-      </c>
-      <c r="O53" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A54" t="s">
-        <v>301</v>
-      </c>
-      <c r="B54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54" t="s">
-        <v>49</v>
-      </c>
-      <c r="E54" t="s">
-        <v>50</v>
-      </c>
-      <c r="F54" t="s">
-        <v>32</v>
       </c>
       <c r="G54" t="s">
         <v>242</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
         <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>302</v>
+        <v>243</v>
       </c>
       <c r="K54" t="s">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="L54" t="s">
         <v>23</v>
@@ -4714,30 +4732,30 @@
         <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.75">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="B55" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D55" t="s">
         <v>30</v>
       </c>
       <c r="E55" t="s">
-        <v>234</v>
+        <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>248</v>
       </c>
       <c r="H55" t="s">
         <v>34</v>
@@ -4746,10 +4764,10 @@
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="K55" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="L55" t="s">
         <v>23</v>
@@ -4758,21 +4776,21 @@
         <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>250</v>
       </c>
       <c r="O55" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.75">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="D56" t="s">
         <v>30</v>
@@ -4781,10 +4799,10 @@
         <v>31</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="G56" t="s">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="H56" t="s">
         <v>34</v>
@@ -4793,10 +4811,10 @@
         <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="K56" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="L56" t="s">
         <v>23</v>
@@ -4808,12 +4826,12 @@
         <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.75">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="B57" t="s">
         <v>71</v>
@@ -4828,198 +4846,198 @@
         <v>31</v>
       </c>
       <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" t="s">
+        <v>258</v>
+      </c>
+      <c r="K57" t="s">
+        <v>147</v>
+      </c>
+      <c r="L57" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" t="s">
+        <v>85</v>
+      </c>
+      <c r="N57" t="s">
+        <v>23</v>
+      </c>
+      <c r="O57" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>260</v>
+      </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" t="s">
+        <v>261</v>
+      </c>
+      <c r="K58" t="s">
+        <v>84</v>
+      </c>
+      <c r="L58" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" t="s">
+        <v>23</v>
+      </c>
+      <c r="O58" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>263</v>
+      </c>
+      <c r="B59" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" t="s">
+        <v>247</v>
+      </c>
+      <c r="D59" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" t="s">
         <v>73</v>
       </c>
-      <c r="G57" t="s">
-        <v>313</v>
-      </c>
-      <c r="H57" t="s">
-        <v>34</v>
-      </c>
-      <c r="I57" t="s">
-        <v>23</v>
-      </c>
-      <c r="J57" t="s">
-        <v>306</v>
-      </c>
-      <c r="K57" t="s">
-        <v>58</v>
-      </c>
-      <c r="L57" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" t="s">
-        <v>23</v>
-      </c>
-      <c r="N57" t="s">
-        <v>314</v>
-      </c>
-      <c r="O57" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A58" t="s">
-        <v>316</v>
-      </c>
-      <c r="B58" t="s">
-        <v>317</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="G59" t="s">
+        <v>264</v>
+      </c>
+      <c r="H59" t="s">
+        <v>34</v>
+      </c>
+      <c r="I59" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" t="s">
+        <v>265</v>
+      </c>
+      <c r="K59" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" t="s">
+        <v>206</v>
+      </c>
+      <c r="O59" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>267</v>
+      </c>
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
         <v>89</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D60" t="s">
         <v>49</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E60" t="s">
         <v>50</v>
       </c>
-      <c r="F58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
-        <v>242</v>
-      </c>
-      <c r="H58" t="s">
-        <v>34</v>
-      </c>
-      <c r="I58" t="s">
-        <v>23</v>
-      </c>
-      <c r="J58" t="s">
-        <v>318</v>
-      </c>
-      <c r="K58" t="s">
-        <v>319</v>
-      </c>
-      <c r="L58" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" t="s">
-        <v>23</v>
-      </c>
-      <c r="N58" t="s">
-        <v>23</v>
-      </c>
-      <c r="O58" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A59" t="s">
-        <v>321</v>
-      </c>
-      <c r="B59" t="s">
-        <v>322</v>
-      </c>
-      <c r="C59" t="s">
-        <v>323</v>
-      </c>
-      <c r="D59" t="s">
-        <v>324</v>
-      </c>
-      <c r="E59" t="s">
-        <v>325</v>
-      </c>
-      <c r="F59" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" t="s">
-        <v>209</v>
-      </c>
-      <c r="H59" t="s">
-        <v>34</v>
-      </c>
-      <c r="I59" t="s">
-        <v>23</v>
-      </c>
-      <c r="J59" t="s">
-        <v>326</v>
-      </c>
-      <c r="K59" t="s">
-        <v>103</v>
-      </c>
-      <c r="L59" t="s">
-        <v>23</v>
-      </c>
-      <c r="M59" t="s">
-        <v>23</v>
-      </c>
-      <c r="N59" t="s">
-        <v>23</v>
-      </c>
-      <c r="O59" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A60" t="s">
-        <v>328</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
+        <v>32</v>
+      </c>
+      <c r="G60" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" t="s">
+        <v>34</v>
+      </c>
+      <c r="I60" t="s">
+        <v>268</v>
+      </c>
+      <c r="J60" t="s">
+        <v>269</v>
+      </c>
+      <c r="K60" t="s">
+        <v>270</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" t="s">
+        <v>23</v>
+      </c>
+      <c r="O60" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" t="s">
         <v>95</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>62</v>
       </c>
-      <c r="D60" t="s">
-        <v>30</v>
-      </c>
-      <c r="E60" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" t="s">
-        <v>329</v>
-      </c>
-      <c r="H60" t="s">
-        <v>34</v>
-      </c>
-      <c r="I60" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" t="s">
-        <v>112</v>
-      </c>
-      <c r="K60" t="s">
-        <v>226</v>
-      </c>
-      <c r="L60" t="s">
-        <v>23</v>
-      </c>
-      <c r="M60" t="s">
-        <v>23</v>
-      </c>
-      <c r="N60" t="s">
-        <v>23</v>
-      </c>
-      <c r="O60" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A61" t="s">
-        <v>331</v>
-      </c>
-      <c r="B61" t="s">
-        <v>317</v>
-      </c>
-      <c r="C61" t="s">
-        <v>89</v>
-      </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F61" t="s">
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>242</v>
+        <v>33</v>
       </c>
       <c r="H61" t="s">
         <v>34</v>
@@ -5028,10 +5046,10 @@
         <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>332</v>
+        <v>273</v>
       </c>
       <c r="K61" t="s">
-        <v>122</v>
+        <v>274</v>
       </c>
       <c r="L61" t="s">
         <v>23</v>
@@ -5043,27 +5061,27 @@
         <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.75">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>334</v>
+        <v>276</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D62" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G62" t="s">
         <v>33</v>
@@ -5075,10 +5093,10 @@
         <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="K62" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="L62" t="s">
         <v>23</v>
@@ -5090,18 +5108,18 @@
         <v>23</v>
       </c>
       <c r="O62" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.75">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>279</v>
       </c>
       <c r="B63" t="s">
-        <v>253</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="D63" t="s">
         <v>30</v>
@@ -5110,10 +5128,10 @@
         <v>31</v>
       </c>
       <c r="F63" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="G63" t="s">
-        <v>337</v>
+        <v>42</v>
       </c>
       <c r="H63" t="s">
         <v>34</v>
@@ -5122,10 +5140,10 @@
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>112</v>
+        <v>280</v>
       </c>
       <c r="K63" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="L63" t="s">
         <v>23</v>
@@ -5137,77 +5155,77 @@
         <v>23</v>
       </c>
       <c r="O63" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.75">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>339</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="D64" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I64" t="s">
         <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="K64" t="s">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="L64" t="s">
         <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N64" t="s">
         <v>23</v>
       </c>
       <c r="O64" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.75">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>343</v>
+        <v>286</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="D65" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
         <v>82</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
         <v>34</v>
@@ -5216,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>344</v>
+        <v>199</v>
       </c>
       <c r="K65" t="s">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="L65" t="s">
         <v>23</v>
@@ -5231,183 +5249,183 @@
         <v>23</v>
       </c>
       <c r="O65" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.75">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="D66" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" t="s">
+        <v>34</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" t="s">
+        <v>290</v>
+      </c>
+      <c r="K66" t="s">
+        <v>291</v>
+      </c>
+      <c r="L66" t="s">
+        <v>23</v>
+      </c>
+      <c r="M66" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" t="s">
+        <v>23</v>
+      </c>
+      <c r="O66" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" t="s">
+        <v>34</v>
+      </c>
+      <c r="I67" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" t="s">
+        <v>294</v>
+      </c>
+      <c r="K67" t="s">
+        <v>175</v>
+      </c>
+      <c r="L67" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>296</v>
+      </c>
+      <c r="B68" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" t="s">
+        <v>62</v>
+      </c>
+      <c r="D68" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" t="s">
+        <v>297</v>
+      </c>
+      <c r="H68" t="s">
+        <v>34</v>
+      </c>
+      <c r="I68" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" t="s">
+        <v>298</v>
+      </c>
+      <c r="K68" t="s">
+        <v>299</v>
+      </c>
+      <c r="L68" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O68" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" t="s">
         <v>49</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E69" t="s">
         <v>50</v>
-      </c>
-      <c r="F66" t="s">
-        <v>32</v>
-      </c>
-      <c r="G66" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" t="s">
-        <v>34</v>
-      </c>
-      <c r="I66" t="s">
-        <v>23</v>
-      </c>
-      <c r="J66" t="s">
-        <v>348</v>
-      </c>
-      <c r="K66" t="s">
-        <v>349</v>
-      </c>
-      <c r="L66" t="s">
-        <v>23</v>
-      </c>
-      <c r="M66" t="s">
-        <v>23</v>
-      </c>
-      <c r="N66" t="s">
-        <v>23</v>
-      </c>
-      <c r="O66" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A67" t="s">
-        <v>351</v>
-      </c>
-      <c r="B67" t="s">
-        <v>352</v>
-      </c>
-      <c r="C67" t="s">
-        <v>353</v>
-      </c>
-      <c r="D67" t="s">
-        <v>181</v>
-      </c>
-      <c r="E67" t="s">
-        <v>182</v>
-      </c>
-      <c r="F67" t="s">
-        <v>144</v>
-      </c>
-      <c r="G67" t="s">
-        <v>354</v>
-      </c>
-      <c r="H67" t="s">
-        <v>34</v>
-      </c>
-      <c r="I67" t="s">
-        <v>23</v>
-      </c>
-      <c r="J67" t="s">
-        <v>355</v>
-      </c>
-      <c r="K67" t="s">
-        <v>194</v>
-      </c>
-      <c r="L67" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67" t="s">
-        <v>23</v>
-      </c>
-      <c r="N67" t="s">
-        <v>23</v>
-      </c>
-      <c r="O67" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A68" t="s">
-        <v>357</v>
-      </c>
-      <c r="B68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C68" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" t="s">
-        <v>31</v>
-      </c>
-      <c r="F68" t="s">
-        <v>32</v>
-      </c>
-      <c r="G68" t="s">
-        <v>33</v>
-      </c>
-      <c r="H68" t="s">
-        <v>34</v>
-      </c>
-      <c r="I68" t="s">
-        <v>23</v>
-      </c>
-      <c r="J68" t="s">
-        <v>358</v>
-      </c>
-      <c r="K68" t="s">
-        <v>103</v>
-      </c>
-      <c r="L68" t="s">
-        <v>23</v>
-      </c>
-      <c r="M68" t="s">
-        <v>23</v>
-      </c>
-      <c r="N68" t="s">
-        <v>23</v>
-      </c>
-      <c r="O68" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A69" t="s">
-        <v>360</v>
-      </c>
-      <c r="B69" t="s">
-        <v>28</v>
-      </c>
-      <c r="C69" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" t="s">
-        <v>30</v>
-      </c>
-      <c r="E69" t="s">
-        <v>31</v>
       </c>
       <c r="F69" t="s">
         <v>32</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="H69" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I69" t="s">
         <v>23</v>
       </c>
       <c r="J69" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="K69" t="s">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="L69" t="s">
         <v>23</v>
@@ -5419,27 +5437,27 @@
         <v>23</v>
       </c>
       <c r="O69" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.75">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>363</v>
+        <v>305</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G70" t="s">
         <v>33</v>
@@ -5451,10 +5469,10 @@
         <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>364</v>
+        <v>306</v>
       </c>
       <c r="K70" t="s">
-        <v>365</v>
+        <v>190</v>
       </c>
       <c r="L70" t="s">
         <v>23</v>
@@ -5466,18 +5484,18 @@
         <v>23</v>
       </c>
       <c r="O70" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.75">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>367</v>
+        <v>308</v>
       </c>
       <c r="B71" t="s">
-        <v>368</v>
+        <v>55</v>
       </c>
       <c r="C71" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="D71" t="s">
         <v>30</v>
@@ -5486,22 +5504,22 @@
         <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>238</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
-        <v>42</v>
+        <v>309</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I71" t="s">
         <v>23</v>
       </c>
       <c r="J71" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="K71" t="s">
-        <v>345</v>
+        <v>113</v>
       </c>
       <c r="L71" t="s">
         <v>23</v>
@@ -5513,18 +5531,18 @@
         <v>23</v>
       </c>
       <c r="O71" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.75">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
-        <v>373</v>
+        <v>72</v>
       </c>
       <c r="D72" t="s">
         <v>30</v>
@@ -5533,10 +5551,10 @@
         <v>31</v>
       </c>
       <c r="F72" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="H72" t="s">
         <v>34</v>
@@ -5545,10 +5563,10 @@
         <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>374</v>
+        <v>306</v>
       </c>
       <c r="K72" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="L72" t="s">
         <v>23</v>
@@ -5557,33 +5575,33 @@
         <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>23</v>
+        <v>314</v>
       </c>
       <c r="O72" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.75">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="B73" t="s">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="C73" t="s">
-        <v>378</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E73" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F73" t="s">
         <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="H73" t="s">
         <v>34</v>
@@ -5592,58 +5610,58 @@
         <v>23</v>
       </c>
       <c r="J73" t="s">
-        <v>379</v>
+        <v>318</v>
       </c>
       <c r="K73" t="s">
+        <v>319</v>
+      </c>
+      <c r="L73" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" t="s">
+        <v>23</v>
+      </c>
+      <c r="O73" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>321</v>
+      </c>
+      <c r="B74" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" t="s">
+        <v>323</v>
+      </c>
+      <c r="D74" t="s">
+        <v>324</v>
+      </c>
+      <c r="E74" t="s">
+        <v>325</v>
+      </c>
+      <c r="F74" t="s">
+        <v>97</v>
+      </c>
+      <c r="G74" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" t="s">
+        <v>34</v>
+      </c>
+      <c r="I74" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" t="s">
+        <v>326</v>
+      </c>
+      <c r="K74" t="s">
         <v>103</v>
       </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" t="s">
-        <v>23</v>
-      </c>
-      <c r="O73" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A74" t="s">
-        <v>381</v>
-      </c>
-      <c r="B74" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" t="s">
-        <v>378</v>
-      </c>
-      <c r="D74" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" t="s">
-        <v>31</v>
-      </c>
-      <c r="F74" t="s">
-        <v>73</v>
-      </c>
-      <c r="G74" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" t="s">
-        <v>34</v>
-      </c>
-      <c r="I74" t="s">
-        <v>23</v>
-      </c>
-      <c r="J74" t="s">
-        <v>382</v>
-      </c>
-      <c r="K74" t="s">
-        <v>165</v>
-      </c>
       <c r="L74" t="s">
         <v>23</v>
       </c>
@@ -5651,21 +5669,21 @@
         <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="O74" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.75">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>384</v>
+        <v>328</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
         <v>30</v>
@@ -5674,10 +5692,10 @@
         <v>31</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>329</v>
       </c>
       <c r="H75" t="s">
         <v>34</v>
@@ -5686,10 +5704,10 @@
         <v>23</v>
       </c>
       <c r="J75" t="s">
-        <v>385</v>
+        <v>112</v>
       </c>
       <c r="K75" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="L75" t="s">
         <v>23</v>
@@ -5701,30 +5719,30 @@
         <v>23</v>
       </c>
       <c r="O75" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.75">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s">
-        <v>197</v>
+        <v>317</v>
       </c>
       <c r="C76" t="s">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>42</v>
+        <v>242</v>
       </c>
       <c r="H76" t="s">
         <v>34</v>
@@ -5733,27 +5751,27 @@
         <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="K76" t="s">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="L76" t="s">
         <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N76" t="s">
         <v>23</v>
       </c>
       <c r="O76" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.75">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="B77" t="s">
         <v>106</v>
@@ -5768,10 +5786,10 @@
         <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="G77" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H77" t="s">
         <v>34</v>
@@ -5780,368 +5798,368 @@
         <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="K77" t="s">
+        <v>92</v>
+      </c>
+      <c r="L77" t="s">
+        <v>23</v>
+      </c>
+      <c r="M77" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" t="s">
+        <v>23</v>
+      </c>
+      <c r="O77" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>336</v>
+      </c>
+      <c r="B78" t="s">
+        <v>253</v>
+      </c>
+      <c r="C78" t="s">
+        <v>254</v>
+      </c>
+      <c r="D78" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" t="s">
+        <v>154</v>
+      </c>
+      <c r="G78" t="s">
+        <v>337</v>
+      </c>
+      <c r="H78" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" t="s">
+        <v>112</v>
+      </c>
+      <c r="K78" t="s">
+        <v>274</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
+      </c>
+      <c r="M78" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" t="s">
+        <v>23</v>
+      </c>
+      <c r="O78" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>339</v>
+      </c>
+      <c r="B79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s">
+        <v>33</v>
+      </c>
+      <c r="H79" t="s">
+        <v>34</v>
+      </c>
+      <c r="I79" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" t="s">
+        <v>340</v>
+      </c>
+      <c r="K79" t="s">
         <v>341</v>
       </c>
-      <c r="L77" t="s">
-        <v>23</v>
-      </c>
-      <c r="M77" t="s">
-        <v>23</v>
-      </c>
-      <c r="N77" t="s">
-        <v>23</v>
-      </c>
-      <c r="O77" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A78" t="s">
-        <v>393</v>
-      </c>
-      <c r="B78" t="s">
-        <v>106</v>
-      </c>
-      <c r="C78" t="s">
-        <v>168</v>
-      </c>
-      <c r="D78" t="s">
-        <v>30</v>
-      </c>
-      <c r="E78" t="s">
-        <v>31</v>
-      </c>
-      <c r="F78" t="s">
-        <v>97</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" t="s">
+        <v>85</v>
+      </c>
+      <c r="N79" t="s">
+        <v>23</v>
+      </c>
+      <c r="O79" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>343</v>
+      </c>
+      <c r="B80" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" t="s">
+        <v>30</v>
+      </c>
+      <c r="E80" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
+        <v>34</v>
+      </c>
+      <c r="I80" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" t="s">
+        <v>344</v>
+      </c>
+      <c r="K80" t="s">
+        <v>345</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80" t="s">
+        <v>85</v>
+      </c>
+      <c r="N80" t="s">
+        <v>23</v>
+      </c>
+      <c r="O80" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>347</v>
+      </c>
+      <c r="B81" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" t="s">
+        <v>49</v>
+      </c>
+      <c r="E81" t="s">
+        <v>50</v>
+      </c>
+      <c r="F81" t="s">
+        <v>32</v>
+      </c>
+      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" t="s">
+        <v>34</v>
+      </c>
+      <c r="I81" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" t="s">
+        <v>348</v>
+      </c>
+      <c r="K81" t="s">
+        <v>349</v>
+      </c>
+      <c r="L81" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" t="s">
+        <v>23</v>
+      </c>
+      <c r="O81" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>351</v>
+      </c>
+      <c r="B82" t="s">
+        <v>352</v>
+      </c>
+      <c r="C82" t="s">
+        <v>353</v>
+      </c>
+      <c r="D82" t="s">
+        <v>181</v>
+      </c>
+      <c r="E82" t="s">
+        <v>182</v>
+      </c>
+      <c r="F82" t="s">
+        <v>144</v>
+      </c>
+      <c r="G82" t="s">
+        <v>354</v>
+      </c>
+      <c r="H82" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" t="s">
+        <v>355</v>
+      </c>
+      <c r="K82" t="s">
+        <v>194</v>
+      </c>
+      <c r="L82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" t="s">
+        <v>23</v>
+      </c>
+      <c r="O82" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>357</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" t="s">
+        <v>32</v>
+      </c>
+      <c r="G83" t="s">
         <v>33</v>
       </c>
-      <c r="H78" t="s">
-        <v>34</v>
-      </c>
-      <c r="I78" t="s">
-        <v>23</v>
-      </c>
-      <c r="J78" t="s">
-        <v>394</v>
-      </c>
-      <c r="K78" t="s">
-        <v>299</v>
-      </c>
-      <c r="L78" t="s">
-        <v>23</v>
-      </c>
-      <c r="M78" t="s">
-        <v>23</v>
-      </c>
-      <c r="N78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O78" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A79" t="s">
-        <v>396</v>
-      </c>
-      <c r="B79" t="s">
-        <v>397</v>
-      </c>
-      <c r="C79" t="s">
-        <v>398</v>
-      </c>
-      <c r="D79" t="s">
-        <v>30</v>
-      </c>
-      <c r="E79" t="s">
-        <v>31</v>
-      </c>
-      <c r="F79" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" t="s">
-        <v>399</v>
-      </c>
-      <c r="H79" t="s">
-        <v>34</v>
-      </c>
-      <c r="I79" t="s">
-        <v>23</v>
-      </c>
-      <c r="J79" t="s">
-        <v>400</v>
-      </c>
-      <c r="K79" t="s">
-        <v>401</v>
-      </c>
-      <c r="L79" t="s">
-        <v>23</v>
-      </c>
-      <c r="M79" t="s">
-        <v>23</v>
-      </c>
-      <c r="N79" t="s">
-        <v>23</v>
-      </c>
-      <c r="O79" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A80" t="s">
-        <v>403</v>
-      </c>
-      <c r="B80" t="s">
-        <v>179</v>
-      </c>
-      <c r="C80" t="s">
-        <v>180</v>
-      </c>
-      <c r="D80" t="s">
-        <v>181</v>
-      </c>
-      <c r="E80" t="s">
-        <v>182</v>
-      </c>
-      <c r="F80" t="s">
-        <v>144</v>
-      </c>
-      <c r="G80" t="s">
-        <v>404</v>
-      </c>
-      <c r="H80" t="s">
-        <v>34</v>
-      </c>
-      <c r="I80" t="s">
-        <v>23</v>
-      </c>
-      <c r="J80" t="s">
-        <v>405</v>
-      </c>
-      <c r="K80" t="s">
-        <v>113</v>
-      </c>
-      <c r="L80" t="s">
-        <v>23</v>
-      </c>
-      <c r="M80" t="s">
-        <v>23</v>
-      </c>
-      <c r="N80" t="s">
-        <v>23</v>
-      </c>
-      <c r="O80" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A81" t="s">
-        <v>407</v>
-      </c>
-      <c r="B81" t="s">
-        <v>408</v>
-      </c>
-      <c r="C81" t="s">
-        <v>409</v>
-      </c>
-      <c r="D81" t="s">
-        <v>30</v>
-      </c>
-      <c r="E81" t="s">
-        <v>31</v>
-      </c>
-      <c r="F81" t="s">
-        <v>82</v>
-      </c>
-      <c r="G81" t="s">
-        <v>42</v>
-      </c>
-      <c r="H81" t="s">
-        <v>34</v>
-      </c>
-      <c r="I81" t="s">
-        <v>23</v>
-      </c>
-      <c r="J81" t="s">
-        <v>410</v>
-      </c>
-      <c r="K81" t="s">
+      <c r="H83" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" t="s">
+        <v>358</v>
+      </c>
+      <c r="K83" t="s">
+        <v>103</v>
+      </c>
+      <c r="L83" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" t="s">
+        <v>23</v>
+      </c>
+      <c r="O83" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>360</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" t="s">
+        <v>32</v>
+      </c>
+      <c r="G84" t="s">
+        <v>33</v>
+      </c>
+      <c r="H84" t="s">
+        <v>34</v>
+      </c>
+      <c r="I84" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" t="s">
+        <v>361</v>
+      </c>
+      <c r="K84" t="s">
         <v>122</v>
       </c>
-      <c r="L81" t="s">
-        <v>23</v>
-      </c>
-      <c r="M81" t="s">
-        <v>85</v>
-      </c>
-      <c r="N81" t="s">
-        <v>23</v>
-      </c>
-      <c r="O81" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A82" t="s">
-        <v>412</v>
-      </c>
-      <c r="B82" t="s">
-        <v>413</v>
-      </c>
-      <c r="C82" t="s">
-        <v>414</v>
-      </c>
-      <c r="D82" t="s">
-        <v>30</v>
-      </c>
-      <c r="E82" t="s">
-        <v>31</v>
-      </c>
-      <c r="F82" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" t="s">
-        <v>33</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
-      </c>
-      <c r="I82" t="s">
-        <v>415</v>
-      </c>
-      <c r="J82" t="s">
-        <v>255</v>
-      </c>
-      <c r="K82" t="s">
-        <v>416</v>
-      </c>
-      <c r="L82" t="s">
-        <v>23</v>
-      </c>
-      <c r="M82" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" t="s">
-        <v>23</v>
-      </c>
-      <c r="O82" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A83" t="s">
-        <v>418</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="L84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>363</v>
+      </c>
+      <c r="B85" t="s">
         <v>150</v>
       </c>
-      <c r="C83" t="s">
-        <v>23</v>
-      </c>
-      <c r="D83" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="C85" t="s">
+        <v>151</v>
+      </c>
+      <c r="D85" t="s">
+        <v>152</v>
+      </c>
+      <c r="E85" t="s">
         <v>153</v>
-      </c>
-      <c r="F83" t="s">
-        <v>73</v>
-      </c>
-      <c r="G83" t="s">
-        <v>21</v>
-      </c>
-      <c r="H83" t="s">
-        <v>22</v>
-      </c>
-      <c r="I83" t="s">
-        <v>23</v>
-      </c>
-      <c r="J83" t="s">
-        <v>419</v>
-      </c>
-      <c r="K83" t="s">
-        <v>36</v>
-      </c>
-      <c r="L83" t="s">
-        <v>23</v>
-      </c>
-      <c r="M83" t="s">
-        <v>23</v>
-      </c>
-      <c r="N83" t="s">
-        <v>420</v>
-      </c>
-      <c r="O83" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A84" t="s">
-        <v>422</v>
-      </c>
-      <c r="B84" t="s">
-        <v>423</v>
-      </c>
-      <c r="C84" t="s">
-        <v>424</v>
-      </c>
-      <c r="D84" t="s">
-        <v>30</v>
-      </c>
-      <c r="E84" t="s">
-        <v>31</v>
-      </c>
-      <c r="F84" t="s">
-        <v>144</v>
-      </c>
-      <c r="G84" t="s">
-        <v>425</v>
-      </c>
-      <c r="H84" t="s">
-        <v>34</v>
-      </c>
-      <c r="I84" t="s">
-        <v>415</v>
-      </c>
-      <c r="J84" t="s">
-        <v>426</v>
-      </c>
-      <c r="K84" t="s">
-        <v>427</v>
-      </c>
-      <c r="L84" t="s">
-        <v>23</v>
-      </c>
-      <c r="M84" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" t="s">
-        <v>23</v>
-      </c>
-      <c r="O84" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A85" t="s">
-        <v>429</v>
-      </c>
-      <c r="B85" t="s">
-        <v>430</v>
-      </c>
-      <c r="C85" t="s">
-        <v>431</v>
-      </c>
-      <c r="D85" t="s">
-        <v>80</v>
-      </c>
-      <c r="E85" t="s">
-        <v>432</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
@@ -6156,10 +6174,10 @@
         <v>23</v>
       </c>
       <c r="J85" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="K85" t="s">
-        <v>44</v>
+        <v>365</v>
       </c>
       <c r="L85" t="s">
         <v>23</v>
@@ -6171,30 +6189,30 @@
         <v>23</v>
       </c>
       <c r="O85" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.75">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>368</v>
       </c>
       <c r="C86" t="s">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F86" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
@@ -6203,33 +6221,33 @@
         <v>23</v>
       </c>
       <c r="J86" t="s">
-        <v>436</v>
+        <v>370</v>
       </c>
       <c r="K86" t="s">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L86" t="s">
         <v>23</v>
       </c>
       <c r="M86" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N86" t="s">
         <v>23</v>
       </c>
       <c r="O86" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.75">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C87" t="s">
-        <v>62</v>
+        <v>373</v>
       </c>
       <c r="D87" t="s">
         <v>30</v>
@@ -6238,69 +6256,69 @@
         <v>31</v>
       </c>
       <c r="F87" t="s">
+        <v>97</v>
+      </c>
+      <c r="G87" t="s">
+        <v>21</v>
+      </c>
+      <c r="H87" t="s">
+        <v>34</v>
+      </c>
+      <c r="I87" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" t="s">
+        <v>374</v>
+      </c>
+      <c r="K87" t="s">
+        <v>185</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" t="s">
+        <v>23</v>
+      </c>
+      <c r="O87" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>376</v>
+      </c>
+      <c r="B88" t="s">
+        <v>377</v>
+      </c>
+      <c r="C88" t="s">
+        <v>378</v>
+      </c>
+      <c r="D88" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" t="s">
         <v>20</v>
-      </c>
-      <c r="G87" t="s">
-        <v>33</v>
-      </c>
-      <c r="H87" t="s">
-        <v>34</v>
-      </c>
-      <c r="I87" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" t="s">
-        <v>306</v>
-      </c>
-      <c r="K87" t="s">
-        <v>274</v>
-      </c>
-      <c r="L87" t="s">
-        <v>23</v>
-      </c>
-      <c r="M87" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" t="s">
-        <v>23</v>
-      </c>
-      <c r="O87" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A88" t="s">
-        <v>440</v>
-      </c>
-      <c r="B88" t="s">
-        <v>150</v>
-      </c>
-      <c r="C88" t="s">
-        <v>441</v>
-      </c>
-      <c r="D88" t="s">
-        <v>152</v>
-      </c>
-      <c r="E88" t="s">
-        <v>153</v>
-      </c>
-      <c r="F88" t="s">
-        <v>442</v>
       </c>
       <c r="G88" t="s">
         <v>33</v>
       </c>
       <c r="H88" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I88" t="s">
         <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>443</v>
+        <v>379</v>
       </c>
       <c r="K88" t="s">
-        <v>444</v>
+        <v>103</v>
       </c>
       <c r="L88" t="s">
         <v>23</v>
@@ -6309,21 +6327,21 @@
         <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="O88" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.75">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>446</v>
+        <v>381</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
-        <v>40</v>
+        <v>378</v>
       </c>
       <c r="D89" t="s">
         <v>30</v>
@@ -6332,10 +6350,10 @@
         <v>31</v>
       </c>
       <c r="F89" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G89" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="H89" t="s">
         <v>34</v>
@@ -6344,33 +6362,33 @@
         <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>447</v>
+        <v>382</v>
       </c>
       <c r="K89" t="s">
-        <v>299</v>
+        <v>165</v>
       </c>
       <c r="L89" t="s">
         <v>23</v>
       </c>
       <c r="M89" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="O89" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.75">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>449</v>
+        <v>384</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D90" t="s">
         <v>30</v>
@@ -6379,7 +6397,7 @@
         <v>31</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G90" t="s">
         <v>33</v>
@@ -6391,10 +6409,10 @@
         <v>23</v>
       </c>
       <c r="J90" t="s">
-        <v>450</v>
+        <v>385</v>
       </c>
       <c r="K90" t="s">
-        <v>451</v>
+        <v>281</v>
       </c>
       <c r="L90" t="s">
         <v>23</v>
@@ -6406,544 +6424,544 @@
         <v>23</v>
       </c>
       <c r="O90" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.75">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>453</v>
+        <v>387</v>
       </c>
       <c r="B91" t="s">
-        <v>454</v>
+        <v>197</v>
       </c>
       <c r="C91" t="s">
-        <v>455</v>
+        <v>198</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" t="s">
+        <v>388</v>
+      </c>
+      <c r="K91" t="s">
+        <v>226</v>
+      </c>
+      <c r="L91" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" t="s">
+        <v>85</v>
+      </c>
+      <c r="N91" t="s">
+        <v>23</v>
+      </c>
+      <c r="O91" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>390</v>
+      </c>
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
+        <v>168</v>
+      </c>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" t="s">
+        <v>238</v>
+      </c>
+      <c r="G92" t="s">
+        <v>42</v>
+      </c>
+      <c r="H92" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" t="s">
+        <v>391</v>
+      </c>
+      <c r="K92" t="s">
+        <v>341</v>
+      </c>
+      <c r="L92" t="s">
+        <v>23</v>
+      </c>
+      <c r="M92" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" t="s">
+        <v>23</v>
+      </c>
+      <c r="O92" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>393</v>
+      </c>
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
+        <v>168</v>
+      </c>
+      <c r="D93" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" t="s">
+        <v>97</v>
+      </c>
+      <c r="G93" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" t="s">
+        <v>394</v>
+      </c>
+      <c r="K93" t="s">
+        <v>299</v>
+      </c>
+      <c r="L93" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" t="s">
+        <v>23</v>
+      </c>
+      <c r="O93" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>396</v>
+      </c>
+      <c r="B94" t="s">
+        <v>397</v>
+      </c>
+      <c r="C94" t="s">
+        <v>398</v>
+      </c>
+      <c r="D94" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" t="s">
+        <v>399</v>
+      </c>
+      <c r="H94" t="s">
+        <v>34</v>
+      </c>
+      <c r="I94" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" t="s">
+        <v>400</v>
+      </c>
+      <c r="K94" t="s">
+        <v>401</v>
+      </c>
+      <c r="L94" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" t="s">
+        <v>23</v>
+      </c>
+      <c r="O94" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>403</v>
+      </c>
+      <c r="B95" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" t="s">
+        <v>181</v>
+      </c>
+      <c r="E95" t="s">
+        <v>182</v>
+      </c>
+      <c r="F95" t="s">
+        <v>144</v>
+      </c>
+      <c r="G95" t="s">
+        <v>404</v>
+      </c>
+      <c r="H95" t="s">
+        <v>34</v>
+      </c>
+      <c r="I95" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" t="s">
+        <v>405</v>
+      </c>
+      <c r="K95" t="s">
+        <v>113</v>
+      </c>
+      <c r="L95" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" t="s">
+        <v>23</v>
+      </c>
+      <c r="O95" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>407</v>
+      </c>
+      <c r="B96" t="s">
+        <v>408</v>
+      </c>
+      <c r="C96" t="s">
+        <v>409</v>
+      </c>
+      <c r="D96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" t="s">
+        <v>82</v>
+      </c>
+      <c r="G96" t="s">
+        <v>42</v>
+      </c>
+      <c r="H96" t="s">
+        <v>34</v>
+      </c>
+      <c r="I96" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" t="s">
+        <v>410</v>
+      </c>
+      <c r="K96" t="s">
+        <v>122</v>
+      </c>
+      <c r="L96" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" t="s">
+        <v>85</v>
+      </c>
+      <c r="N96" t="s">
+        <v>23</v>
+      </c>
+      <c r="O96" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>412</v>
+      </c>
+      <c r="B97" t="s">
+        <v>413</v>
+      </c>
+      <c r="C97" t="s">
+        <v>414</v>
+      </c>
+      <c r="D97" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
+        <v>415</v>
+      </c>
+      <c r="J97" t="s">
+        <v>255</v>
+      </c>
+      <c r="K97" t="s">
+        <v>416</v>
+      </c>
+      <c r="L97" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" t="s">
+        <v>23</v>
+      </c>
+      <c r="O97" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>418</v>
+      </c>
+      <c r="B98" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" t="s">
+        <v>153</v>
+      </c>
+      <c r="F98" t="s">
+        <v>73</v>
+      </c>
+      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="H98" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" t="s">
+        <v>419</v>
+      </c>
+      <c r="K98" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" t="s">
+        <v>23</v>
+      </c>
+      <c r="M98" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" t="s">
+        <v>420</v>
+      </c>
+      <c r="O98" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>422</v>
+      </c>
+      <c r="B99" t="s">
+        <v>423</v>
+      </c>
+      <c r="C99" t="s">
+        <v>424</v>
+      </c>
+      <c r="D99" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" t="s">
+        <v>31</v>
+      </c>
+      <c r="F99" t="s">
+        <v>144</v>
+      </c>
+      <c r="G99" t="s">
+        <v>425</v>
+      </c>
+      <c r="H99" t="s">
+        <v>34</v>
+      </c>
+      <c r="I99" t="s">
+        <v>415</v>
+      </c>
+      <c r="J99" t="s">
+        <v>426</v>
+      </c>
+      <c r="K99" t="s">
+        <v>427</v>
+      </c>
+      <c r="L99" t="s">
+        <v>23</v>
+      </c>
+      <c r="M99" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" t="s">
+        <v>23</v>
+      </c>
+      <c r="O99" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>429</v>
+      </c>
+      <c r="B100" t="s">
+        <v>430</v>
+      </c>
+      <c r="C100" t="s">
+        <v>431</v>
+      </c>
+      <c r="D100" t="s">
+        <v>80</v>
+      </c>
+      <c r="E100" t="s">
+        <v>432</v>
+      </c>
+      <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>33</v>
+      </c>
+      <c r="H100" t="s">
+        <v>34</v>
+      </c>
+      <c r="I100" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" t="s">
+        <v>433</v>
+      </c>
+      <c r="K100" t="s">
+        <v>44</v>
+      </c>
+      <c r="L100" t="s">
+        <v>23</v>
+      </c>
+      <c r="M100" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" t="s">
+        <v>23</v>
+      </c>
+      <c r="O100" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>435</v>
+      </c>
+      <c r="B101" t="s">
+        <v>78</v>
+      </c>
+      <c r="C101" t="s">
+        <v>79</v>
+      </c>
+      <c r="D101" t="s">
+        <v>80</v>
+      </c>
+      <c r="E101" t="s">
         <v>81</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F101" t="s">
+        <v>82</v>
+      </c>
+      <c r="G101" t="s">
+        <v>33</v>
+      </c>
+      <c r="H101" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" t="s">
+        <v>436</v>
+      </c>
+      <c r="K101" t="s">
+        <v>134</v>
+      </c>
+      <c r="L101" t="s">
+        <v>23</v>
+      </c>
+      <c r="M101" t="s">
+        <v>85</v>
+      </c>
+      <c r="N101" t="s">
+        <v>23</v>
+      </c>
+      <c r="O101" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>438</v>
+      </c>
+      <c r="B102" t="s">
+        <v>95</v>
+      </c>
+      <c r="C102" t="s">
+        <v>62</v>
+      </c>
+      <c r="D102" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" t="s">
         <v>20</v>
-      </c>
-      <c r="G91" t="s">
-        <v>242</v>
-      </c>
-      <c r="H91" t="s">
-        <v>22</v>
-      </c>
-      <c r="I91" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" t="s">
-        <v>456</v>
-      </c>
-      <c r="K91" t="s">
-        <v>416</v>
-      </c>
-      <c r="L91" t="s">
-        <v>23</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" t="s">
-        <v>23</v>
-      </c>
-      <c r="O91" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A92" t="s">
-        <v>458</v>
-      </c>
-      <c r="B92" t="s">
-        <v>377</v>
-      </c>
-      <c r="C92" t="s">
-        <v>378</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>31</v>
-      </c>
-      <c r="F92" t="s">
-        <v>41</v>
-      </c>
-      <c r="G92" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" t="s">
-        <v>34</v>
-      </c>
-      <c r="I92" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" t="s">
-        <v>459</v>
-      </c>
-      <c r="K92" t="s">
-        <v>200</v>
-      </c>
-      <c r="L92" t="s">
-        <v>23</v>
-      </c>
-      <c r="M92" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" t="s">
-        <v>23</v>
-      </c>
-      <c r="O92" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A93" t="s">
-        <v>461</v>
-      </c>
-      <c r="B93" t="s">
-        <v>377</v>
-      </c>
-      <c r="C93" t="s">
-        <v>378</v>
-      </c>
-      <c r="D93" t="s">
-        <v>30</v>
-      </c>
-      <c r="E93" t="s">
-        <v>31</v>
-      </c>
-      <c r="F93" t="s">
-        <v>41</v>
-      </c>
-      <c r="G93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H93" t="s">
-        <v>34</v>
-      </c>
-      <c r="I93" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" t="s">
-        <v>391</v>
-      </c>
-      <c r="K93" t="s">
-        <v>345</v>
-      </c>
-      <c r="L93" t="s">
-        <v>23</v>
-      </c>
-      <c r="M93" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" t="s">
-        <v>23</v>
-      </c>
-      <c r="O93" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A94" t="s">
-        <v>463</v>
-      </c>
-      <c r="B94" t="s">
-        <v>464</v>
-      </c>
-      <c r="C94" t="s">
-        <v>465</v>
-      </c>
-      <c r="D94" t="s">
-        <v>466</v>
-      </c>
-      <c r="E94" t="s">
-        <v>467</v>
-      </c>
-      <c r="F94" t="s">
-        <v>82</v>
-      </c>
-      <c r="G94" t="s">
-        <v>33</v>
-      </c>
-      <c r="H94" t="s">
-        <v>34</v>
-      </c>
-      <c r="I94" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" t="s">
-        <v>468</v>
-      </c>
-      <c r="K94" t="s">
-        <v>113</v>
-      </c>
-      <c r="L94" t="s">
-        <v>23</v>
-      </c>
-      <c r="M94" t="s">
-        <v>85</v>
-      </c>
-      <c r="N94" t="s">
-        <v>23</v>
-      </c>
-      <c r="O94" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A95" t="s">
-        <v>470</v>
-      </c>
-      <c r="B95" t="s">
-        <v>95</v>
-      </c>
-      <c r="C95" t="s">
-        <v>62</v>
-      </c>
-      <c r="D95" t="s">
-        <v>30</v>
-      </c>
-      <c r="E95" t="s">
-        <v>31</v>
-      </c>
-      <c r="F95" t="s">
-        <v>20</v>
-      </c>
-      <c r="G95" t="s">
-        <v>33</v>
-      </c>
-      <c r="H95" t="s">
-        <v>34</v>
-      </c>
-      <c r="I95" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" t="s">
-        <v>471</v>
-      </c>
-      <c r="K95" t="s">
-        <v>64</v>
-      </c>
-      <c r="L95" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" t="s">
-        <v>23</v>
-      </c>
-      <c r="N95" t="s">
-        <v>23</v>
-      </c>
-      <c r="O95" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A96" t="s">
-        <v>473</v>
-      </c>
-      <c r="B96" t="s">
-        <v>28</v>
-      </c>
-      <c r="C96" t="s">
-        <v>29</v>
-      </c>
-      <c r="D96" t="s">
-        <v>30</v>
-      </c>
-      <c r="E96" t="s">
-        <v>31</v>
-      </c>
-      <c r="F96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G96" t="s">
-        <v>33</v>
-      </c>
-      <c r="H96" t="s">
-        <v>34</v>
-      </c>
-      <c r="I96" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" t="s">
-        <v>474</v>
-      </c>
-      <c r="K96" t="s">
-        <v>475</v>
-      </c>
-      <c r="L96" t="s">
-        <v>23</v>
-      </c>
-      <c r="M96" t="s">
-        <v>23</v>
-      </c>
-      <c r="N96" t="s">
-        <v>23</v>
-      </c>
-      <c r="O96" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A97" t="s">
-        <v>477</v>
-      </c>
-      <c r="B97" t="s">
-        <v>28</v>
-      </c>
-      <c r="C97" t="s">
-        <v>29</v>
-      </c>
-      <c r="D97" t="s">
-        <v>30</v>
-      </c>
-      <c r="E97" t="s">
-        <v>31</v>
-      </c>
-      <c r="F97" t="s">
-        <v>32</v>
-      </c>
-      <c r="G97" t="s">
-        <v>42</v>
-      </c>
-      <c r="H97" t="s">
-        <v>34</v>
-      </c>
-      <c r="I97" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" t="s">
-        <v>478</v>
-      </c>
-      <c r="K97" t="s">
-        <v>479</v>
-      </c>
-      <c r="L97" t="s">
-        <v>23</v>
-      </c>
-      <c r="M97" t="s">
-        <v>23</v>
-      </c>
-      <c r="N97" t="s">
-        <v>23</v>
-      </c>
-      <c r="O97" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A98" t="s">
-        <v>481</v>
-      </c>
-      <c r="B98" t="s">
-        <v>95</v>
-      </c>
-      <c r="C98" t="s">
-        <v>96</v>
-      </c>
-      <c r="D98" t="s">
-        <v>31</v>
-      </c>
-      <c r="E98" t="s">
-        <v>31</v>
-      </c>
-      <c r="F98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" t="s">
-        <v>42</v>
-      </c>
-      <c r="H98" t="s">
-        <v>34</v>
-      </c>
-      <c r="I98" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" t="s">
-        <v>482</v>
-      </c>
-      <c r="K98" t="s">
-        <v>226</v>
-      </c>
-      <c r="L98" t="s">
-        <v>23</v>
-      </c>
-      <c r="M98" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" t="s">
-        <v>23</v>
-      </c>
-      <c r="O98" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A99" t="s">
-        <v>484</v>
-      </c>
-      <c r="B99" t="s">
-        <v>413</v>
-      </c>
-      <c r="C99" t="s">
-        <v>168</v>
-      </c>
-      <c r="D99" t="s">
-        <v>30</v>
-      </c>
-      <c r="E99" t="s">
-        <v>31</v>
-      </c>
-      <c r="F99" t="s">
-        <v>20</v>
-      </c>
-      <c r="G99" t="s">
-        <v>33</v>
-      </c>
-      <c r="H99" t="s">
-        <v>34</v>
-      </c>
-      <c r="I99" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" t="s">
-        <v>485</v>
-      </c>
-      <c r="K99" t="s">
-        <v>117</v>
-      </c>
-      <c r="L99" t="s">
-        <v>23</v>
-      </c>
-      <c r="M99" t="s">
-        <v>23</v>
-      </c>
-      <c r="N99" t="s">
-        <v>23</v>
-      </c>
-      <c r="O99" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A100" t="s">
-        <v>487</v>
-      </c>
-      <c r="B100" t="s">
-        <v>397</v>
-      </c>
-      <c r="C100" t="s">
-        <v>398</v>
-      </c>
-      <c r="D100" t="s">
-        <v>30</v>
-      </c>
-      <c r="E100" t="s">
-        <v>31</v>
-      </c>
-      <c r="F100" t="s">
-        <v>82</v>
-      </c>
-      <c r="G100" t="s">
-        <v>42</v>
-      </c>
-      <c r="H100" t="s">
-        <v>34</v>
-      </c>
-      <c r="I100" t="s">
-        <v>488</v>
-      </c>
-      <c r="J100" t="s">
-        <v>306</v>
-      </c>
-      <c r="K100" t="s">
-        <v>113</v>
-      </c>
-      <c r="L100" t="s">
-        <v>23</v>
-      </c>
-      <c r="M100" t="s">
-        <v>85</v>
-      </c>
-      <c r="N100" t="s">
-        <v>23</v>
-      </c>
-      <c r="O100" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A101" t="s">
-        <v>490</v>
-      </c>
-      <c r="B101" t="s">
-        <v>397</v>
-      </c>
-      <c r="C101" t="s">
-        <v>398</v>
-      </c>
-      <c r="D101" t="s">
-        <v>30</v>
-      </c>
-      <c r="E101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F101" t="s">
-        <v>154</v>
-      </c>
-      <c r="G101" t="s">
-        <v>242</v>
-      </c>
-      <c r="H101" t="s">
-        <v>34</v>
-      </c>
-      <c r="I101" t="s">
-        <v>488</v>
-      </c>
-      <c r="J101" t="s">
-        <v>400</v>
-      </c>
-      <c r="K101" t="s">
-        <v>349</v>
-      </c>
-      <c r="L101" t="s">
-        <v>23</v>
-      </c>
-      <c r="M101" t="s">
-        <v>23</v>
-      </c>
-      <c r="N101" t="s">
-        <v>23</v>
-      </c>
-      <c r="O101" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A102" t="s">
-        <v>492</v>
-      </c>
-      <c r="B102" t="s">
-        <v>28</v>
-      </c>
-      <c r="C102" t="s">
-        <v>29</v>
-      </c>
-      <c r="D102" t="s">
-        <v>30</v>
-      </c>
-      <c r="E102" t="s">
-        <v>31</v>
-      </c>
-      <c r="F102" t="s">
-        <v>32</v>
       </c>
       <c r="G102" t="s">
         <v>33</v>
@@ -6955,10 +6973,10 @@
         <v>23</v>
       </c>
       <c r="J102" t="s">
-        <v>493</v>
+        <v>306</v>
       </c>
       <c r="K102" t="s">
-        <v>416</v>
+        <v>274</v>
       </c>
       <c r="L102" t="s">
         <v>23</v>
@@ -6970,42 +6988,42 @@
         <v>23</v>
       </c>
       <c r="O102" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.75">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>495</v>
+        <v>440</v>
       </c>
       <c r="B103" t="s">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="C103" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="D103" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="E103" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F103" t="s">
-        <v>144</v>
+        <v>442</v>
       </c>
       <c r="G103" t="s">
-        <v>496</v>
+        <v>33</v>
       </c>
       <c r="H103" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I103" t="s">
-        <v>415</v>
+        <v>23</v>
       </c>
       <c r="J103" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="K103" t="s">
-        <v>274</v>
+        <v>444</v>
       </c>
       <c r="L103" t="s">
         <v>23</v>
@@ -7014,74 +7032,74 @@
         <v>23</v>
       </c>
       <c r="N103" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="O103" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.75">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>499</v>
+        <v>446</v>
       </c>
       <c r="B104" t="s">
-        <v>500</v>
+        <v>39</v>
       </c>
       <c r="C104" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D104" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E104" t="s">
         <v>31</v>
       </c>
       <c r="F104" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G104" t="s">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="H104" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I104" t="s">
         <v>23</v>
       </c>
       <c r="J104" t="s">
-        <v>501</v>
+        <v>447</v>
       </c>
       <c r="K104" t="s">
-        <v>64</v>
+        <v>299</v>
       </c>
       <c r="L104" t="s">
         <v>23</v>
       </c>
       <c r="M104" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="N104" t="s">
         <v>23</v>
       </c>
       <c r="O104" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.75">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
       <c r="B105" t="s">
-        <v>322</v>
+        <v>55</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>324</v>
+        <v>30</v>
       </c>
       <c r="E105" t="s">
-        <v>325</v>
+        <v>31</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -7096,10 +7114,10 @@
         <v>23</v>
       </c>
       <c r="J105" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="K105" t="s">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="L105" t="s">
         <v>23</v>
@@ -7111,133 +7129,133 @@
         <v>23</v>
       </c>
       <c r="O105" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.75">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>507</v>
+        <v>453</v>
       </c>
       <c r="B106" t="s">
-        <v>197</v>
+        <v>454</v>
       </c>
       <c r="C106" t="s">
-        <v>198</v>
+        <v>455</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="F106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>242</v>
+      </c>
+      <c r="H106" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" t="s">
+        <v>456</v>
+      </c>
+      <c r="K106" t="s">
+        <v>416</v>
+      </c>
+      <c r="L106" t="s">
+        <v>23</v>
+      </c>
+      <c r="M106" t="s">
+        <v>23</v>
+      </c>
+      <c r="N106" t="s">
+        <v>23</v>
+      </c>
+      <c r="O106" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>458</v>
+      </c>
+      <c r="B107" t="s">
+        <v>377</v>
+      </c>
+      <c r="C107" t="s">
+        <v>378</v>
+      </c>
+      <c r="D107" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" t="s">
+        <v>31</v>
+      </c>
+      <c r="F107" t="s">
         <v>41</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G107" t="s">
+        <v>21</v>
+      </c>
+      <c r="H107" t="s">
+        <v>34</v>
+      </c>
+      <c r="I107" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" t="s">
+        <v>459</v>
+      </c>
+      <c r="K107" t="s">
+        <v>200</v>
+      </c>
+      <c r="L107" t="s">
+        <v>23</v>
+      </c>
+      <c r="M107" t="s">
+        <v>23</v>
+      </c>
+      <c r="N107" t="s">
+        <v>23</v>
+      </c>
+      <c r="O107" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>461</v>
+      </c>
+      <c r="B108" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" t="s">
+        <v>378</v>
+      </c>
+      <c r="D108" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" t="s">
+        <v>31</v>
+      </c>
+      <c r="F108" t="s">
+        <v>41</v>
+      </c>
+      <c r="G108" t="s">
         <v>42</v>
       </c>
-      <c r="H106" t="s">
-        <v>34</v>
-      </c>
-      <c r="I106" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" t="s">
-        <v>508</v>
-      </c>
-      <c r="K106" t="s">
-        <v>509</v>
-      </c>
-      <c r="L106" t="s">
-        <v>23</v>
-      </c>
-      <c r="M106" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" t="s">
-        <v>23</v>
-      </c>
-      <c r="O106" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A107" t="s">
-        <v>511</v>
-      </c>
-      <c r="B107" t="s">
-        <v>95</v>
-      </c>
-      <c r="C107" t="s">
-        <v>62</v>
-      </c>
-      <c r="D107" t="s">
-        <v>30</v>
-      </c>
-      <c r="E107" t="s">
-        <v>31</v>
-      </c>
-      <c r="F107" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" t="s">
-        <v>242</v>
-      </c>
-      <c r="H107" t="s">
-        <v>34</v>
-      </c>
-      <c r="I107" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" t="s">
-        <v>512</v>
-      </c>
-      <c r="K107" t="s">
-        <v>64</v>
-      </c>
-      <c r="L107" t="s">
-        <v>23</v>
-      </c>
-      <c r="M107" t="s">
-        <v>23</v>
-      </c>
-      <c r="N107" t="s">
-        <v>23</v>
-      </c>
-      <c r="O107" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A108" t="s">
-        <v>514</v>
-      </c>
-      <c r="B108" t="s">
-        <v>515</v>
-      </c>
-      <c r="C108" t="s">
-        <v>516</v>
-      </c>
-      <c r="D108" t="s">
-        <v>30</v>
-      </c>
-      <c r="E108" t="s">
-        <v>31</v>
-      </c>
-      <c r="F108" t="s">
-        <v>20</v>
-      </c>
-      <c r="G108" t="s">
-        <v>33</v>
-      </c>
       <c r="H108" t="s">
         <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>517</v>
+        <v>23</v>
       </c>
       <c r="J108" t="s">
-        <v>518</v>
+        <v>391</v>
       </c>
       <c r="K108" t="s">
         <v>345</v>
@@ -7252,30 +7270,30 @@
         <v>23</v>
       </c>
       <c r="O108" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.75">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>520</v>
+        <v>463</v>
       </c>
       <c r="B109" t="s">
-        <v>246</v>
+        <v>464</v>
       </c>
       <c r="C109" t="s">
-        <v>247</v>
+        <v>465</v>
       </c>
       <c r="D109" t="s">
-        <v>30</v>
+        <v>466</v>
       </c>
       <c r="E109" t="s">
-        <v>31</v>
+        <v>467</v>
       </c>
       <c r="F109" t="s">
         <v>82</v>
       </c>
       <c r="G109" t="s">
-        <v>521</v>
+        <v>33</v>
       </c>
       <c r="H109" t="s">
         <v>34</v>
@@ -7284,10 +7302,10 @@
         <v>23</v>
       </c>
       <c r="J109" t="s">
-        <v>522</v>
+        <v>468</v>
       </c>
       <c r="K109" t="s">
-        <v>523</v>
+        <v>113</v>
       </c>
       <c r="L109" t="s">
         <v>23</v>
@@ -7299,18 +7317,18 @@
         <v>23</v>
       </c>
       <c r="O109" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.75">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>525</v>
+        <v>470</v>
       </c>
       <c r="B110" t="s">
-        <v>377</v>
+        <v>95</v>
       </c>
       <c r="C110" t="s">
-        <v>378</v>
+        <v>62</v>
       </c>
       <c r="D110" t="s">
         <v>30</v>
@@ -7319,10 +7337,10 @@
         <v>31</v>
       </c>
       <c r="F110" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G110" t="s">
-        <v>526</v>
+        <v>33</v>
       </c>
       <c r="H110" t="s">
         <v>34</v>
@@ -7331,10 +7349,10 @@
         <v>23</v>
       </c>
       <c r="J110" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="K110" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="L110" t="s">
         <v>23</v>
@@ -7346,15 +7364,15 @@
         <v>23</v>
       </c>
       <c r="O110" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.75">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="B111" t="s">
-        <v>413</v>
+        <v>28</v>
       </c>
       <c r="C111" t="s">
         <v>29</v>
@@ -7366,10 +7384,10 @@
         <v>31</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G111" t="s">
-        <v>530</v>
+        <v>33</v>
       </c>
       <c r="H111" t="s">
         <v>34</v>
@@ -7378,10 +7396,10 @@
         <v>23</v>
       </c>
       <c r="J111" t="s">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="K111" t="s">
-        <v>532</v>
+        <v>475</v>
       </c>
       <c r="L111" t="s">
         <v>23</v>
@@ -7393,18 +7411,18 @@
         <v>23</v>
       </c>
       <c r="O111" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.75">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>534</v>
+        <v>477</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="C112" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="D112" t="s">
         <v>30</v>
@@ -7413,22 +7431,22 @@
         <v>31</v>
       </c>
       <c r="F112" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="G112" t="s">
-        <v>535</v>
+        <v>42</v>
       </c>
       <c r="H112" t="s">
         <v>34</v>
       </c>
       <c r="I112" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="J112" t="s">
-        <v>536</v>
+        <v>478</v>
       </c>
       <c r="K112" t="s">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="L112" t="s">
         <v>23</v>
@@ -7440,21 +7458,21 @@
         <v>23</v>
       </c>
       <c r="O112" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.75">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>539</v>
+        <v>481</v>
       </c>
       <c r="B113" t="s">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E113" t="s">
         <v>31</v>
@@ -7463,19 +7481,19 @@
         <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>541</v>
+        <v>42</v>
       </c>
       <c r="H113" t="s">
         <v>34</v>
       </c>
       <c r="I113" t="s">
-        <v>542</v>
+        <v>23</v>
       </c>
       <c r="J113" t="s">
-        <v>543</v>
+        <v>482</v>
       </c>
       <c r="K113" t="s">
-        <v>537</v>
+        <v>226</v>
       </c>
       <c r="L113" t="s">
         <v>23</v>
@@ -7487,18 +7505,18 @@
         <v>23</v>
       </c>
       <c r="O113" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.75">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>545</v>
+        <v>484</v>
       </c>
       <c r="B114" t="s">
-        <v>215</v>
+        <v>413</v>
       </c>
       <c r="C114" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="D114" t="s">
         <v>30</v>
@@ -7507,304 +7525,304 @@
         <v>31</v>
       </c>
       <c r="F114" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" t="s">
+        <v>34</v>
+      </c>
+      <c r="I114" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" t="s">
+        <v>485</v>
+      </c>
+      <c r="K114" t="s">
+        <v>117</v>
+      </c>
+      <c r="L114" t="s">
+        <v>23</v>
+      </c>
+      <c r="M114" t="s">
+        <v>23</v>
+      </c>
+      <c r="N114" t="s">
+        <v>23</v>
+      </c>
+      <c r="O114" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>487</v>
+      </c>
+      <c r="B115" t="s">
+        <v>397</v>
+      </c>
+      <c r="C115" t="s">
+        <v>398</v>
+      </c>
+      <c r="D115" t="s">
+        <v>30</v>
+      </c>
+      <c r="E115" t="s">
+        <v>31</v>
+      </c>
+      <c r="F115" t="s">
+        <v>82</v>
+      </c>
+      <c r="G115" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" t="s">
+        <v>34</v>
+      </c>
+      <c r="I115" t="s">
+        <v>488</v>
+      </c>
+      <c r="J115" t="s">
+        <v>306</v>
+      </c>
+      <c r="K115" t="s">
+        <v>113</v>
+      </c>
+      <c r="L115" t="s">
+        <v>23</v>
+      </c>
+      <c r="M115" t="s">
+        <v>85</v>
+      </c>
+      <c r="N115" t="s">
+        <v>23</v>
+      </c>
+      <c r="O115" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>490</v>
+      </c>
+      <c r="B116" t="s">
+        <v>397</v>
+      </c>
+      <c r="C116" t="s">
+        <v>398</v>
+      </c>
+      <c r="D116" t="s">
+        <v>30</v>
+      </c>
+      <c r="E116" t="s">
+        <v>31</v>
+      </c>
+      <c r="F116" t="s">
+        <v>154</v>
+      </c>
+      <c r="G116" t="s">
+        <v>242</v>
+      </c>
+      <c r="H116" t="s">
+        <v>34</v>
+      </c>
+      <c r="I116" t="s">
+        <v>488</v>
+      </c>
+      <c r="J116" t="s">
+        <v>400</v>
+      </c>
+      <c r="K116" t="s">
+        <v>349</v>
+      </c>
+      <c r="L116" t="s">
+        <v>23</v>
+      </c>
+      <c r="M116" t="s">
+        <v>23</v>
+      </c>
+      <c r="N116" t="s">
+        <v>23</v>
+      </c>
+      <c r="O116" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>492</v>
+      </c>
+      <c r="B117" t="s">
+        <v>28</v>
+      </c>
+      <c r="C117" t="s">
+        <v>29</v>
+      </c>
+      <c r="D117" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" t="s">
+        <v>31</v>
+      </c>
+      <c r="F117" t="s">
+        <v>32</v>
+      </c>
+      <c r="G117" t="s">
+        <v>33</v>
+      </c>
+      <c r="H117" t="s">
+        <v>34</v>
+      </c>
+      <c r="I117" t="s">
+        <v>23</v>
+      </c>
+      <c r="J117" t="s">
+        <v>493</v>
+      </c>
+      <c r="K117" t="s">
+        <v>416</v>
+      </c>
+      <c r="L117" t="s">
+        <v>23</v>
+      </c>
+      <c r="M117" t="s">
+        <v>23</v>
+      </c>
+      <c r="N117" t="s">
+        <v>23</v>
+      </c>
+      <c r="O117" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>495</v>
+      </c>
+      <c r="B118" t="s">
+        <v>423</v>
+      </c>
+      <c r="C118" t="s">
+        <v>424</v>
+      </c>
+      <c r="D118" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" t="s">
+        <v>31</v>
+      </c>
+      <c r="F118" t="s">
         <v>144</v>
       </c>
-      <c r="G114" t="s">
-        <v>535</v>
-      </c>
-      <c r="H114" t="s">
-        <v>34</v>
-      </c>
-      <c r="I114" t="s">
-        <v>488</v>
-      </c>
-      <c r="J114" t="s">
-        <v>546</v>
-      </c>
-      <c r="K114" t="s">
-        <v>547</v>
-      </c>
-      <c r="L114" t="s">
-        <v>23</v>
-      </c>
-      <c r="M114" t="s">
-        <v>23</v>
-      </c>
-      <c r="N114" t="s">
-        <v>23</v>
-      </c>
-      <c r="O114" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A115" t="s">
-        <v>549</v>
-      </c>
-      <c r="B115" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" t="s">
-        <v>96</v>
-      </c>
-      <c r="D115" t="s">
-        <v>31</v>
-      </c>
-      <c r="E115" t="s">
-        <v>31</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="G118" t="s">
+        <v>496</v>
+      </c>
+      <c r="H118" t="s">
+        <v>34</v>
+      </c>
+      <c r="I118" t="s">
+        <v>415</v>
+      </c>
+      <c r="J118" t="s">
+        <v>497</v>
+      </c>
+      <c r="K118" t="s">
+        <v>274</v>
+      </c>
+      <c r="L118" t="s">
+        <v>23</v>
+      </c>
+      <c r="M118" t="s">
+        <v>23</v>
+      </c>
+      <c r="N118" t="s">
+        <v>23</v>
+      </c>
+      <c r="O118" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>499</v>
+      </c>
+      <c r="B119" t="s">
+        <v>500</v>
+      </c>
+      <c r="C119" t="s">
+        <v>23</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119" t="s">
+        <v>31</v>
+      </c>
+      <c r="F119" t="s">
+        <v>32</v>
+      </c>
+      <c r="G119" t="s">
+        <v>33</v>
+      </c>
+      <c r="H119" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" t="s">
+        <v>23</v>
+      </c>
+      <c r="J119" t="s">
+        <v>501</v>
+      </c>
+      <c r="K119" t="s">
+        <v>64</v>
+      </c>
+      <c r="L119" t="s">
+        <v>23</v>
+      </c>
+      <c r="M119" t="s">
+        <v>23</v>
+      </c>
+      <c r="N119" t="s">
+        <v>23</v>
+      </c>
+      <c r="O119" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>503</v>
+      </c>
+      <c r="B120" t="s">
+        <v>322</v>
+      </c>
+      <c r="C120" t="s">
+        <v>323</v>
+      </c>
+      <c r="D120" t="s">
+        <v>324</v>
+      </c>
+      <c r="E120" t="s">
+        <v>325</v>
+      </c>
+      <c r="F120" t="s">
         <v>20</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G120" t="s">
         <v>33</v>
       </c>
-      <c r="H115" t="s">
-        <v>34</v>
-      </c>
-      <c r="I115" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" t="s">
-        <v>550</v>
-      </c>
-      <c r="K115" t="s">
-        <v>92</v>
-      </c>
-      <c r="L115" t="s">
-        <v>23</v>
-      </c>
-      <c r="M115" t="s">
-        <v>23</v>
-      </c>
-      <c r="N115" t="s">
-        <v>23</v>
-      </c>
-      <c r="O115" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A116" t="s">
-        <v>552</v>
-      </c>
-      <c r="B116" t="s">
-        <v>423</v>
-      </c>
-      <c r="C116" t="s">
-        <v>424</v>
-      </c>
-      <c r="D116" t="s">
-        <v>30</v>
-      </c>
-      <c r="E116" t="s">
-        <v>31</v>
-      </c>
-      <c r="F116" t="s">
-        <v>82</v>
-      </c>
-      <c r="G116" t="s">
-        <v>42</v>
-      </c>
-      <c r="H116" t="s">
-        <v>34</v>
-      </c>
-      <c r="I116" t="s">
-        <v>415</v>
-      </c>
-      <c r="J116" t="s">
-        <v>553</v>
-      </c>
-      <c r="K116" t="s">
-        <v>554</v>
-      </c>
-      <c r="L116" t="s">
-        <v>23</v>
-      </c>
-      <c r="M116" t="s">
-        <v>85</v>
-      </c>
-      <c r="N116" t="s">
-        <v>23</v>
-      </c>
-      <c r="O116" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A117" t="s">
-        <v>556</v>
-      </c>
-      <c r="B117" t="s">
-        <v>557</v>
-      </c>
-      <c r="C117" t="s">
-        <v>558</v>
-      </c>
-      <c r="D117" t="s">
-        <v>152</v>
-      </c>
-      <c r="E117" t="s">
-        <v>153</v>
-      </c>
-      <c r="F117" t="s">
-        <v>144</v>
-      </c>
-      <c r="G117" t="s">
-        <v>559</v>
-      </c>
-      <c r="H117" t="s">
-        <v>34</v>
-      </c>
-      <c r="I117" t="s">
-        <v>23</v>
-      </c>
-      <c r="J117" t="s">
-        <v>560</v>
-      </c>
-      <c r="K117" t="s">
-        <v>532</v>
-      </c>
-      <c r="L117" t="s">
-        <v>23</v>
-      </c>
-      <c r="M117" t="s">
-        <v>23</v>
-      </c>
-      <c r="N117" t="s">
-        <v>23</v>
-      </c>
-      <c r="O117" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A118" t="s">
-        <v>562</v>
-      </c>
-      <c r="B118" t="s">
-        <v>232</v>
-      </c>
-      <c r="C118" t="s">
-        <v>233</v>
-      </c>
-      <c r="D118" t="s">
-        <v>30</v>
-      </c>
-      <c r="E118" t="s">
-        <v>234</v>
-      </c>
-      <c r="F118" t="s">
-        <v>20</v>
-      </c>
-      <c r="G118" t="s">
-        <v>169</v>
-      </c>
-      <c r="H118" t="s">
-        <v>34</v>
-      </c>
-      <c r="I118" t="s">
-        <v>542</v>
-      </c>
-      <c r="J118" t="s">
-        <v>563</v>
-      </c>
-      <c r="K118" t="s">
-        <v>25</v>
-      </c>
-      <c r="L118" t="s">
-        <v>23</v>
-      </c>
-      <c r="M118" t="s">
-        <v>23</v>
-      </c>
-      <c r="N118" t="s">
-        <v>23</v>
-      </c>
-      <c r="O118" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A119" t="s">
-        <v>565</v>
-      </c>
-      <c r="B119" t="s">
-        <v>515</v>
-      </c>
-      <c r="C119" t="s">
-        <v>516</v>
-      </c>
-      <c r="D119" t="s">
-        <v>30</v>
-      </c>
-      <c r="E119" t="s">
-        <v>31</v>
-      </c>
-      <c r="F119" t="s">
-        <v>20</v>
-      </c>
-      <c r="G119" t="s">
-        <v>42</v>
-      </c>
-      <c r="H119" t="s">
-        <v>34</v>
-      </c>
-      <c r="I119" t="s">
-        <v>517</v>
-      </c>
-      <c r="J119" t="s">
-        <v>566</v>
-      </c>
-      <c r="K119" t="s">
-        <v>567</v>
-      </c>
-      <c r="L119" t="s">
-        <v>23</v>
-      </c>
-      <c r="M119" t="s">
-        <v>23</v>
-      </c>
-      <c r="N119" t="s">
-        <v>23</v>
-      </c>
-      <c r="O119" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A120" t="s">
-        <v>569</v>
-      </c>
-      <c r="B120" t="s">
-        <v>570</v>
-      </c>
-      <c r="C120" t="s">
-        <v>441</v>
-      </c>
-      <c r="D120" t="s">
-        <v>152</v>
-      </c>
-      <c r="E120" t="s">
-        <v>571</v>
-      </c>
-      <c r="F120" t="s">
-        <v>572</v>
-      </c>
-      <c r="G120" t="s">
-        <v>23</v>
-      </c>
       <c r="H120" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
         <v>23</v>
       </c>
       <c r="J120" t="s">
-        <v>573</v>
+        <v>504</v>
       </c>
       <c r="K120" t="s">
-        <v>122</v>
+        <v>505</v>
       </c>
       <c r="L120" t="s">
         <v>23</v>
@@ -7816,42 +7834,42 @@
         <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.75">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>575</v>
+        <v>507</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="C121" t="s">
-        <v>126</v>
+        <v>198</v>
       </c>
       <c r="D121" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F121" t="s">
         <v>41</v>
       </c>
       <c r="G121" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H121" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
         <v>23</v>
       </c>
       <c r="J121" t="s">
-        <v>576</v>
+        <v>508</v>
       </c>
       <c r="K121" t="s">
-        <v>194</v>
+        <v>509</v>
       </c>
       <c r="L121" t="s">
         <v>23</v>
@@ -7863,18 +7881,18 @@
         <v>23</v>
       </c>
       <c r="O121" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.75">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>578</v>
+        <v>511</v>
       </c>
       <c r="B122" t="s">
-        <v>397</v>
+        <v>95</v>
       </c>
       <c r="C122" t="s">
-        <v>398</v>
+        <v>62</v>
       </c>
       <c r="D122" t="s">
         <v>30</v>
@@ -7886,66 +7904,66 @@
         <v>20</v>
       </c>
       <c r="G122" t="s">
+        <v>242</v>
+      </c>
+      <c r="H122" t="s">
+        <v>34</v>
+      </c>
+      <c r="I122" t="s">
+        <v>23</v>
+      </c>
+      <c r="J122" t="s">
+        <v>512</v>
+      </c>
+      <c r="K122" t="s">
+        <v>64</v>
+      </c>
+      <c r="L122" t="s">
+        <v>23</v>
+      </c>
+      <c r="M122" t="s">
+        <v>23</v>
+      </c>
+      <c r="N122" t="s">
+        <v>23</v>
+      </c>
+      <c r="O122" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>514</v>
+      </c>
+      <c r="B123" t="s">
+        <v>515</v>
+      </c>
+      <c r="C123" t="s">
+        <v>516</v>
+      </c>
+      <c r="D123" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" t="s">
+        <v>31</v>
+      </c>
+      <c r="F123" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" t="s">
         <v>33</v>
       </c>
-      <c r="H122" t="s">
-        <v>34</v>
-      </c>
-      <c r="I122" t="s">
-        <v>23</v>
-      </c>
-      <c r="J122" t="s">
-        <v>579</v>
-      </c>
-      <c r="K122" t="s">
-        <v>416</v>
-      </c>
-      <c r="L122" t="s">
-        <v>23</v>
-      </c>
-      <c r="M122" t="s">
-        <v>23</v>
-      </c>
-      <c r="N122" t="s">
-        <v>23</v>
-      </c>
-      <c r="O122" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.75">
-      <c r="A123" t="s">
-        <v>581</v>
-      </c>
-      <c r="B123" t="s">
-        <v>423</v>
-      </c>
-      <c r="C123" t="s">
-        <v>424</v>
-      </c>
-      <c r="D123" t="s">
-        <v>30</v>
-      </c>
-      <c r="E123" t="s">
-        <v>31</v>
-      </c>
-      <c r="F123" t="s">
-        <v>144</v>
-      </c>
-      <c r="G123" t="s">
-        <v>404</v>
-      </c>
       <c r="H123" t="s">
         <v>34</v>
       </c>
       <c r="I123" t="s">
-        <v>415</v>
+        <v>517</v>
       </c>
       <c r="J123" t="s">
-        <v>582</v>
+        <v>518</v>
       </c>
       <c r="K123" t="s">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="L123" t="s">
         <v>23</v>
@@ -7957,65 +7975,65 @@
         <v>23</v>
       </c>
       <c r="O123" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.75">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>584</v>
+        <v>520</v>
       </c>
       <c r="B124" t="s">
-        <v>585</v>
+        <v>246</v>
       </c>
       <c r="C124" t="s">
-        <v>48</v>
+        <v>247</v>
       </c>
       <c r="D124" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E124" t="s">
         <v>31</v>
       </c>
       <c r="F124" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G124" t="s">
-        <v>586</v>
+        <v>521</v>
       </c>
       <c r="H124" t="s">
         <v>34</v>
       </c>
       <c r="I124" t="s">
-        <v>517</v>
+        <v>23</v>
       </c>
       <c r="J124" t="s">
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="K124" t="s">
+        <v>523</v>
+      </c>
+      <c r="L124" t="s">
+        <v>23</v>
+      </c>
+      <c r="M124" t="s">
         <v>85</v>
       </c>
-      <c r="L124" t="s">
-        <v>23</v>
-      </c>
-      <c r="M124" t="s">
-        <v>23</v>
-      </c>
       <c r="N124" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="O124" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.75">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>589</v>
+        <v>525</v>
       </c>
       <c r="B125" t="s">
-        <v>246</v>
+        <v>377</v>
       </c>
       <c r="C125" t="s">
-        <v>247</v>
+        <v>378</v>
       </c>
       <c r="D125" t="s">
         <v>30</v>
@@ -8024,10 +8042,10 @@
         <v>31</v>
       </c>
       <c r="F125" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G125" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H125" t="s">
         <v>34</v>
@@ -8036,36 +8054,36 @@
         <v>23</v>
       </c>
       <c r="J125" t="s">
-        <v>590</v>
+        <v>527</v>
       </c>
       <c r="K125" t="s">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="L125" t="s">
         <v>23</v>
       </c>
       <c r="M125" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N125" t="s">
         <v>23</v>
       </c>
       <c r="O125" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.75">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>592</v>
+        <v>529</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="D126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E126" t="s">
         <v>31</v>
@@ -8074,7 +8092,7 @@
         <v>20</v>
       </c>
       <c r="G126" t="s">
-        <v>33</v>
+        <v>530</v>
       </c>
       <c r="H126" t="s">
         <v>34</v>
@@ -8083,10 +8101,10 @@
         <v>23</v>
       </c>
       <c r="J126" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="K126" t="s">
-        <v>281</v>
+        <v>532</v>
       </c>
       <c r="L126" t="s">
         <v>23</v>
@@ -8098,7 +8116,54 @@
         <v>23</v>
       </c>
       <c r="O126" t="s">
-        <v>594</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>534</v>
+      </c>
+      <c r="B127" t="s">
+        <v>215</v>
+      </c>
+      <c r="C127" t="s">
+        <v>216</v>
+      </c>
+      <c r="D127" t="s">
+        <v>30</v>
+      </c>
+      <c r="E127" t="s">
+        <v>31</v>
+      </c>
+      <c r="F127" t="s">
+        <v>144</v>
+      </c>
+      <c r="G127" t="s">
+        <v>535</v>
+      </c>
+      <c r="H127" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" t="s">
+        <v>488</v>
+      </c>
+      <c r="J127" t="s">
+        <v>536</v>
+      </c>
+      <c r="K127" t="s">
+        <v>537</v>
+      </c>
+      <c r="L127" t="s">
+        <v>23</v>
+      </c>
+      <c r="M127" t="s">
+        <v>23</v>
+      </c>
+      <c r="N127" t="s">
+        <v>23</v>
+      </c>
+      <c r="O127" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F62E682-C746-4917-8339-5612AA86346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63019E19-8FEE-4654-A5D4-E8927FDB089F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="647">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,618 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/03/2026 9:10:05 AM</t>
+  </si>
+  <si>
+    <t>7054 Houston</t>
+  </si>
+  <si>
+    <t>John Thomason</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Houston, TX</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Dave Huber</t>
+  </si>
+  <si>
+    <t>10002 Rowlett Road, Houston, TX, 77075</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544553ae-01d4-545e-ac73-eb60f33a66bc</t>
+  </si>
+  <si>
+    <t>04/02/2026 3:07:06 PM</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>4979 Clinton Drive, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454fce-8181-517c-a549-a4650e3dafc8</t>
+  </si>
+  <si>
+    <t>04/02/2026 9:33:59 AM</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>South Freeway, Manvel, TX, 77578</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454e9d-855d-5ea3-9aba-237e142f8001</t>
+  </si>
+  <si>
+    <t>04/01/2026 5:33:17 PM</t>
+  </si>
+  <si>
+    <t>Almeda Road, Houston, TX, 77054</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b2d-fb29-5e9c-a2d3-cf21b6007f59</t>
+  </si>
+  <si>
+    <t>04/01/2026 3:17:02 PM</t>
+  </si>
+  <si>
+    <t>6457 San Diego</t>
+  </si>
+  <si>
+    <t>Diego Padilla</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>HAAS Alert, San Diego, CA</t>
+  </si>
+  <si>
+    <t>Lane Departure</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>San Diego Freeway, San Diego, CA, 92173</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454ab1-3bf2-5232-ab41-13dd555f2a9d</t>
+  </si>
+  <si>
+    <t>04/01/2026 2:25:12 PM</t>
+  </si>
+  <si>
+    <t>4172 Laredo</t>
+  </si>
+  <si>
+    <t>Daniel Alvarado</t>
+  </si>
+  <si>
+    <t>Laredo, TX</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Laredo, TX</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>I 35;US 83, Laredo, TX, 78045</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454a81-c709-55b8-9043-7b475a3738ea</t>
+  </si>
+  <si>
+    <t>04/01/2026 1:24:52 PM</t>
+  </si>
+  <si>
+    <t>4751 Edinburg</t>
+  </si>
+  <si>
+    <t>Ramon Torres</t>
+  </si>
+  <si>
+    <t>Edinburg, TX, Falfurrias, TX</t>
+  </si>
+  <si>
+    <t>Edinburg, TX, HAAS Alert</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>9408 FM 491, 8.0 mi SW Raymondville, Willacy County, TX, 78569</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454a4a-8a11-5a83-aa7a-561414d108a4</t>
+  </si>
+  <si>
+    <t>04/01/2026 11:08:47 AM</t>
+  </si>
+  <si>
+    <t>2713 Tucson</t>
+  </si>
+  <si>
+    <t>Albino Dominguez</t>
+  </si>
+  <si>
+    <t>Nogales, AZ</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Tucson, AZ</t>
+  </si>
+  <si>
+    <t>Guy N Henderson - Tucson</t>
+  </si>
+  <si>
+    <t>1367 North Grand Avenue, Nogales, AZ, 85621</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544549cd-f4b1-505e-9387-0c84705e232a</t>
+  </si>
+  <si>
+    <t>03/31/2026 6:32:56 PM</t>
+  </si>
+  <si>
+    <t>6458 San Diego</t>
+  </si>
+  <si>
+    <t>Miguel Camba</t>
+  </si>
+  <si>
+    <t>Harsh Turn</t>
+  </si>
+  <si>
+    <t>3704 Beyer Boulevard, San Diego, CA, 92173</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445463e-3be6-5c4e-a286-905b11d28436</t>
+  </si>
+  <si>
+    <t>03/31/2026 6:08:06 PM</t>
+  </si>
+  <si>
+    <t>9000 Almeda Road, Houston, TX, 77054</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454627-7eef-5c9d-94f4-678f5ca42697</t>
+  </si>
+  <si>
+    <t>03/31/2026 2:32:14 PM</t>
+  </si>
+  <si>
+    <t>7053 Houston</t>
+  </si>
+  <si>
+    <t>Graylyn Norman</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Emergency Siren, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>9723 South Freeway, Houston, TX, 77045</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454561-da9d-512b-af9b-ef5f1056cf6a</t>
+  </si>
+  <si>
+    <t>03/31/2026 11:23:23 AM</t>
+  </si>
+  <si>
+    <t>7056 Houston</t>
+  </si>
+  <si>
+    <t>Roy Hyson</t>
+  </si>
+  <si>
+    <t>8100 Gulf Freeway, Houston, TX, 77017</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544544b4-f584-5f91-b174-9621a630adec</t>
+  </si>
+  <si>
+    <t>03/30/2026 7:24:10 PM</t>
+  </si>
+  <si>
+    <t>2699 Tucson</t>
+  </si>
+  <si>
+    <t>Luis Ochoa</t>
+  </si>
+  <si>
+    <t>2801 North Grand Avenue, Nogales, AZ, 85621</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454146-c443-5910-a191-a0d3f35d3299</t>
+  </si>
+  <si>
+    <t>03/30/2026 4:02:01 PM</t>
+  </si>
+  <si>
+    <t>TX 44, Robstown, TX, 78339</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445408d-b211-5921-ab88-e6493e92b9b4</t>
+  </si>
+  <si>
+    <t>03/30/2026 10:20:48 AM</t>
+  </si>
+  <si>
+    <t>5503 Houston</t>
+  </si>
+  <si>
+    <t>Forward Collision Warning</t>
+  </si>
+  <si>
+    <t>Congested</t>
+  </si>
+  <si>
+    <t>5043 Gulf Freeway, Houston, TX, 77023</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f55-4cf6-5d8c-98c4-6a73ef21b49d</t>
+  </si>
+  <si>
+    <t>03/27/2026 11:33:03 AM</t>
+  </si>
+  <si>
+    <t>South Freeway, Houston, TX, 77047</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453024-5f1b-5d08-9a63-fb99b9b65c91</t>
+  </si>
+  <si>
+    <t>03/27/2026 7:32:49 AM</t>
+  </si>
+  <si>
+    <t>6421 Laredo</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>471 TX 285, Hebbronville, TX, 78361</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452f48-6dd5-5182-acf1-c53535b1eb9a</t>
+  </si>
+  <si>
+    <t>03/26/2026 4:34:48 PM</t>
+  </si>
+  <si>
+    <t>4748 El Paso</t>
+  </si>
+  <si>
+    <t>Nicholas Perez</t>
+  </si>
+  <si>
+    <t>El Paso, TX</t>
+  </si>
+  <si>
+    <t>El Paso, TX, HAAS Alert</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>East Vinton Road, Westway Number 2 Colonia, TX, 79821</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c12-4532-598e-9540-8d2ff9064c99</t>
+  </si>
+  <si>
+    <t>03/26/2026 12:27:51 PM</t>
+  </si>
+  <si>
+    <t>6065 Edinburg</t>
+  </si>
+  <si>
+    <t>Bentura Moreno</t>
+  </si>
+  <si>
+    <t>Edinburg, TX</t>
+  </si>
+  <si>
+    <t>Edinburg, TX, HAAS Alert, Service Trucks</t>
+  </si>
+  <si>
+    <t>Passengers, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 2;US 83, Alamo, TX, 78516</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b30-2e3b-562e-9623-00fd5f5aaa37</t>
+  </si>
+  <si>
+    <t>03/25/2026 1:58:02 PM</t>
+  </si>
+  <si>
+    <t>Mathew Sumners</t>
+  </si>
+  <si>
+    <t>12308 Fuqua Street, Houston, TX, 77034</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445265c-62f0-5a30-9f78-0e965473426d</t>
+  </si>
+  <si>
+    <t>03/25/2026 4:27:58 AM</t>
+  </si>
+  <si>
+    <t>8682 Houston</t>
+  </si>
+  <si>
+    <t>RudyRodriguez</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Northwest Freeway, Houston, TX, 77092-7005</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452452-79b5-5b86-ab7a-7d2cf1ede108</t>
+  </si>
+  <si>
+    <t>03/24/2026 5:36:25 PM</t>
+  </si>
+  <si>
+    <t>7052 Houston</t>
+  </si>
+  <si>
+    <t>Antony Ashley</t>
+  </si>
+  <si>
+    <t>South Loop West, Houston, TX, 77054</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544521fd-f93c-5cfc-bf4b-eda4db3200bd</t>
+  </si>
+  <si>
+    <t>03/24/2026 12:18:03 PM</t>
+  </si>
+  <si>
+    <t>2715 Houston</t>
+  </si>
+  <si>
+    <t>Southwest Freeway Frontage Road, Houston, TX, 77046</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544520da-7f25-55fe-8055-cbfe201979e7</t>
+  </si>
+  <si>
+    <t>03/23/2026 4:21:48 PM</t>
+  </si>
+  <si>
+    <t>4858 Houston</t>
+  </si>
+  <si>
+    <t>Ronald Ryans</t>
+  </si>
+  <si>
+    <t>East Loop North, Houston, TX, 77029</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c93-4b3c-5ae0-96d1-31d6e9c7b502</t>
+  </si>
+  <si>
+    <t>03/23/2026 3:18:41 PM</t>
+  </si>
+  <si>
+    <t>8361 Tucson</t>
+  </si>
+  <si>
+    <t>Guy Henderson</t>
+  </si>
+  <si>
+    <t>Nogales, AZ, Tucson, AZ, Yuma, AZ</t>
+  </si>
+  <si>
+    <t>South Kings Highway, 5.1 mi W Douglas, Cochise County, AZ, 85626</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c59-81c0-5847-99f6-c62a9f458e43</t>
+  </si>
+  <si>
+    <t>03/23/2026 9:48:17 AM</t>
+  </si>
+  <si>
+    <t>5438 El Paso</t>
+  </si>
+  <si>
+    <t>Northwest Freeway Frontage Road, Jersey Village, TX, 77065:77429</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451b2b-04df-590c-a501-10db316e8507</t>
+  </si>
+  <si>
+    <t>03/22/2026 3:30:41 AM</t>
+  </si>
+  <si>
+    <t>2716 Houston</t>
+  </si>
+  <si>
+    <t>Jason Albert</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>North Loop West, Houston, TX, 77008</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544514aa-f384-571b-bb40-c7e71c4e5e98</t>
+  </si>
+  <si>
+    <t>03/21/2026 3:12:04 PM</t>
+  </si>
+  <si>
+    <t>Christopher Keefe</t>
+  </si>
+  <si>
+    <t>North Freeway, Houston, TX, 77037</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451206-bb58-5166-ab43-97b58c8dac3d</t>
+  </si>
+  <si>
+    <t>03/20/2026 2:10:51 PM</t>
+  </si>
+  <si>
+    <t>Todd Johnston</t>
+  </si>
+  <si>
+    <t>I 35;US 77, Bellmead, TX, 76705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450ca8-53ba-58de-b474-e36e7dfe067f</t>
+  </si>
+  <si>
+    <t>03/20/2026 11:11:41 AM</t>
+  </si>
+  <si>
+    <t>Jesus Gutierrez</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Construction, Pedestrians, Light Traffic</t>
+  </si>
+  <si>
+    <t>2755 Clinton Drive, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450c04-4b4f-5269-9e3d-ecded278ae39</t>
+  </si>
+  <si>
+    <t>03/20/2026 10:30:12 AM</t>
+  </si>
+  <si>
+    <t>El Cibolo Road, Faysville, TX</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450bde-4fc5-5ad7-b1ad-b3af4a64bdc4</t>
+  </si>
+  <si>
+    <t>03/20/2026 7:11:29 AM</t>
+  </si>
+  <si>
+    <t>0189 Houston</t>
+  </si>
+  <si>
+    <t>Russell McKenzie</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>4957 Hull Street, Houston, TX, 77021</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b28-624c-5700-8145-29c59b89af40</t>
+  </si>
+  <si>
     <t>03/18/2026 11:55:52 PM</t>
   </si>
   <si>
@@ -71,24 +683,9 @@
     <t>Carlos Arispe</t>
   </si>
   <si>
-    <t>Laredo, TX</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Laredo, TX</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>2314 Jacaman Road, Laredo, TX, 78041</t>
   </si>
   <si>
@@ -101,27 +698,6 @@
     <t>03/18/2026 5:10:13 PM</t>
   </si>
   <si>
-    <t>7054 Houston</t>
-  </si>
-  <si>
-    <t>John Thomason</t>
-  </si>
-  <si>
-    <t>Houston, TX</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Houston, TX</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>10028 Rowlett Road, Houston, TX, 77075</t>
   </si>
   <si>
@@ -140,18 +716,9 @@
     <t>Felipe Andrade</t>
   </si>
   <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>I 45, Marshy Springs, TX, 75831</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fcf2-ef79-55c6-8742-994353030b03</t>
   </si>
   <si>
@@ -164,12 +731,6 @@
     <t>Oscar Rodriguez</t>
   </si>
   <si>
-    <t>El Paso, TX</t>
-  </si>
-  <si>
-    <t>El Paso, TX, HAAS Alert</t>
-  </si>
-  <si>
     <t>Woodrow Bean Transmountain Drive, El Paso, TX, 79924</t>
   </si>
   <si>
@@ -182,9 +743,6 @@
     <t>03/16/2026 6:57:54 PM</t>
   </si>
   <si>
-    <t>5503 Houston</t>
-  </si>
-  <si>
     <t>Deandre Smith</t>
   </si>
   <si>
@@ -200,12 +758,6 @@
     <t>03/16/2026 6:45:52 PM</t>
   </si>
   <si>
-    <t>2715 Houston</t>
-  </si>
-  <si>
-    <t>Christopher Keefe</t>
-  </si>
-  <si>
     <t>2197 Wilson Road, Humble, TX, 77396</t>
   </si>
   <si>
@@ -230,15 +782,6 @@
     <t>03/16/2026 3:27:42 PM</t>
   </si>
   <si>
-    <t>2716 Houston</t>
-  </si>
-  <si>
-    <t>Jason Albert</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>West Bellfort Street, 0.6 mi W Four Corners, Fort Bend County, TX, 77469</t>
   </si>
   <si>
@@ -257,36 +800,15 @@
     <t>Miguel Limon-Cadena</t>
   </si>
   <si>
-    <t>Edinburg, TX</t>
-  </si>
-  <si>
-    <t>Edinburg, TX, HAAS Alert</t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>1898 South 23rd Street, McAllen, TX, 78503</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f7c3-36ae-56a0-98f3-cfd114cda669</t>
   </si>
   <si>
     <t>03/16/2026 7:16:14 AM</t>
   </si>
   <si>
-    <t>4748 El Paso</t>
-  </si>
-  <si>
-    <t>Nicholas Perez</t>
-  </si>
-  <si>
     <t>Congested, Night</t>
   </si>
   <si>
@@ -305,9 +827,6 @@
     <t>4240 Houston</t>
   </si>
   <si>
-    <t>Roy Hyson</t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
@@ -326,18 +845,12 @@
     <t>9399 Cullen Boulevard, Houston, TX, 77051</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f1d9-c1c6-5423-bae0-f9d249c20615</t>
   </si>
   <si>
     <t>03/13/2026 8:33:15 PM</t>
   </si>
   <si>
-    <t>8682 Houston</t>
-  </si>
-  <si>
     <t>2966 South Loop West Frontage Road, Houston, TX, 77054</t>
   </si>
   <si>
@@ -350,9 +863,6 @@
     <t>03/13/2026 7:22:44 PM</t>
   </si>
   <si>
-    <t>Jesus Gutierrez</t>
-  </si>
-  <si>
     <t>South Freeway, Houston, TX, 77004</t>
   </si>
   <si>
@@ -398,9 +908,6 @@
     <t>Aaron Torres-Cano</t>
   </si>
   <si>
-    <t>Edinburg, TX, Falfurrias, TX</t>
-  </si>
-  <si>
     <t>US 281-R Business, 3.6 mi S Alice, Jim Wells County, TX, 78333</t>
   </si>
   <si>
@@ -410,12 +917,6 @@
     <t>03/11/2026 7:42:50 PM</t>
   </si>
   <si>
-    <t>4858 Houston</t>
-  </si>
-  <si>
-    <t>Ronald Ryans</t>
-  </si>
-  <si>
     <t>Gulf Freeway, Houston, TX, 77010</t>
   </si>
   <si>
@@ -437,21 +938,12 @@
     <t>Wayside Drive, Houston, TX, 77020</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb2f-6b1e-5c71-8fa3-c884543b8c18</t>
   </si>
   <si>
     <t>03/06/2026 7:09:44 PM</t>
   </si>
   <si>
-    <t>Antony Ashley</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Very Drowsy, Moderate Traffic</t>
   </si>
   <si>
@@ -464,30 +956,6 @@
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c5d7-dc54-5e7c-9c65-1bb2d1270b0d</t>
   </si>
   <si>
-    <t>03/06/2026 11:33:57 AM</t>
-  </si>
-  <si>
-    <t>6458 San Diego</t>
-  </si>
-  <si>
-    <t>Miguel Camba</t>
-  </si>
-  <si>
-    <t>San Diego, CA</t>
-  </si>
-  <si>
-    <t>HAAS Alert, San Diego, CA</t>
-  </si>
-  <si>
-    <t>Lane Departure</t>
-  </si>
-  <si>
-    <t>Otay Mesa Road, San Diego, CA, 92179</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c436-9690-5a98-97d6-7187984eecc7</t>
-  </si>
-  <si>
     <t>03/06/2026 9:29:24 AM</t>
   </si>
   <si>
@@ -512,9 +980,6 @@
     <t>3891 South Loop West Frontage Road, Houston, TX, 77025</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c066-c98f-5a1e-8688-152c8e7ef922</t>
   </si>
   <si>
@@ -524,9 +989,6 @@
     <t>Eric Sanchez</t>
   </si>
   <si>
-    <t>Congested</t>
-  </si>
-  <si>
     <t>10150 Southwest Freeway, Houston, TX, 77074</t>
   </si>
   <si>
@@ -536,7 +998,7 @@
     <t>03/04/2026 4:34:23 PM</t>
   </si>
   <si>
-    <t>Harsh Turn</t>
+    <t>Andrea M Savoie</t>
   </si>
   <si>
     <t>Otay Lakes Road, 4.6 mi S Jamul, San Diego County, CA</t>
@@ -587,9 +1049,6 @@
     <t>FM 2812, Edinburg, TX, 78542</t>
   </si>
   <si>
-    <t>53</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b90e-1330-5272-b272-228b9e2d71f7</t>
   </si>
   <si>
@@ -608,15 +1067,6 @@
     <t>03/03/2026 9:52:27 AM</t>
   </si>
   <si>
-    <t>4172 Laredo</t>
-  </si>
-  <si>
-    <t>Daniel Alvarado</t>
-  </si>
-  <si>
-    <t>I 35;US 83, Laredo, TX, 78045</t>
-  </si>
-  <si>
     <t>62</t>
   </si>
   <si>
@@ -695,9 +1145,6 @@
     <t>Cypresswood Drive, Fairfield, TX, 77433</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445aaff-6416-5cf8-83de-80272efdf60f</t>
   </si>
   <si>
@@ -731,9 +1178,6 @@
     <t>02/27/2026 11:23:14 AM</t>
   </si>
   <si>
-    <t>Forward Collision Warning</t>
-  </si>
-  <si>
     <t>4709 Bissonnet Street, Bellaire, TX, 77401</t>
   </si>
   <si>
@@ -743,9 +1187,6 @@
     <t>02/26/2026 9:38:19 AM</t>
   </si>
   <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
     <t>North Interstate 35E, Carrollton, TX, 75006</t>
   </si>
   <si>
@@ -755,12 +1196,6 @@
     <t>02/25/2026 3:21:09 PM</t>
   </si>
   <si>
-    <t>7053 Houston</t>
-  </si>
-  <si>
-    <t>Graylyn Norman</t>
-  </si>
-  <si>
     <t>Emergency Siren, Light Traffic</t>
   </si>
   <si>
@@ -782,9 +1217,6 @@
     <t>Virgil McGeorge</t>
   </si>
   <si>
-    <t>Almeda Road, Houston, TX, 77054</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459311-f679-5879-8252-b0b3821e4149</t>
   </si>
   <si>
@@ -860,9 +1292,6 @@
     <t>7799 Monroe Road, Houston, TX, 77061</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544572a4-3a33-5f56-ba43-e7aabdbdb0e0</t>
   </si>
   <si>
@@ -914,9 +1343,6 @@
     <t>5280 TX 146, Baytown, TX, 77523</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544561bc-0c15-568a-9493-a7bd0f2754b6</t>
   </si>
   <si>
@@ -974,9 +1400,6 @@
     <t>Border West Expressway, El Paso, TX, 79968</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544552fe-996d-5caa-9add-d41f34cfefbf</t>
   </si>
   <si>
@@ -1079,9 +1502,6 @@
     <t>Adrian Valencia</t>
   </si>
   <si>
-    <t>Very Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
     <t>CA 86, 11.0 mi SSE Oasis, Imperial County, CA, 92274-8498</t>
   </si>
   <si>
@@ -1112,9 +1532,6 @@
     <t>CA 125 Toll, 1.6 mi SW La Presa, San Diego County, CA, 91239</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452632-f344-5d85-ac81-b9d1f6099b8a</t>
   </si>
   <si>
@@ -1208,21 +1625,6 @@
     <t>01/28/2026 1:16:27 PM</t>
   </si>
   <si>
-    <t>0189 Houston</t>
-  </si>
-  <si>
-    <t>Russell McKenzie</t>
-  </si>
-  <si>
-    <t>Passengers, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>South Loop West, Houston, TX, 77054</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450609-20c7-5de2-991d-327466ba0824</t>
   </si>
   <si>
@@ -1262,9 +1664,6 @@
     <t>Virgil Russel</t>
   </si>
   <si>
-    <t>Dave Huber</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
@@ -1298,24 +1697,12 @@
     <t>Northwest Freeway HOV, Houston, TX, 77092</t>
   </si>
   <si>
-    <t>52</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f00b-4cc0-5923-b258-f47a1d4dfa9b</t>
   </si>
   <si>
     <t>01/23/2026 4:24:17 PM</t>
   </si>
   <si>
-    <t>6065 Edinburg</t>
-  </si>
-  <si>
-    <t>Bentura Moreno</t>
-  </si>
-  <si>
-    <t>Edinburg, TX, HAAS Alert, Service Trucks</t>
-  </si>
-  <si>
     <t>I 69C;US 281, Edinburg, TX, 78542</t>
   </si>
   <si>
@@ -1346,9 +1733,6 @@
     <t>Harsh Accel</t>
   </si>
   <si>
-    <t>3704 Beyer Boulevard, San Diego, CA, 92173</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1379,12 +1763,6 @@
     <t>01/19/2026 1:49:37 PM</t>
   </si>
   <si>
-    <t>4751 Edinburg</t>
-  </si>
-  <si>
-    <t>Ramon Torres</t>
-  </si>
-  <si>
     <t>Military Highway, Hidalgo, TX, 78557</t>
   </si>
   <si>
@@ -1418,9 +1796,6 @@
     <t>Tucson, AZ</t>
   </si>
   <si>
-    <t>HAAS Alert, Tucson, AZ</t>
-  </si>
-  <si>
     <t>11732 West Ajo Highway, Robles Junction, AZ, 85735</t>
   </si>
   <si>
@@ -1454,9 +1829,6 @@
     <t>West Broadway Street, Pearland, TX, 74404</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b99b-b797-5e27-b416-05ef05a4d462</t>
   </si>
   <si>
@@ -1568,9 +1940,6 @@
     <t>Michael Hanvy</t>
   </si>
   <si>
-    <t>Andrea M Savoie</t>
-  </si>
-  <si>
     <t>12299 Gulf Freeway, Houston, TX, 77034</t>
   </si>
   <si>
@@ -1580,9 +1949,6 @@
     <t>01/06/2026 11:33:34 AM</t>
   </si>
   <si>
-    <t>Emergency Siren, Moderate Traffic</t>
-  </si>
-  <si>
     <t>South Loop West, Houston, TX, 77051</t>
   </si>
   <si>
@@ -1590,234 +1956,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445945f-085a-53d0-b4bd-b0f0bcc3be63</t>
-  </si>
-  <si>
-    <t>01/01/2026 4:48:16 PM</t>
-  </si>
-  <si>
-    <t>Construction, Pedestrians, Light Traffic</t>
-  </si>
-  <si>
-    <t>2112 Leeland Street, Houston, TX, 77003</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457bbf-5b4f-5108-8b90-6eebaaecd9d9</t>
-  </si>
-  <si>
-    <t>12/31/2025 9:02:58 AM</t>
-  </si>
-  <si>
-    <t>Construction, Passengers, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>3464 FM 521, Arcola, TX, 77545</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574ee-fead-572d-bd84-2e04d3a47fd2</t>
-  </si>
-  <si>
-    <t>12/29/2025 11:30:34 AM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Light Traffic</t>
-  </si>
-  <si>
-    <t>11801 Gulf Freeway, Houston, TX, 77034</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b29-6792-5ba3-a1fe-059df342f346</t>
-  </si>
-  <si>
-    <t>7052 Houston</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
-    <t>03/26/2026 4:34:48 PM</t>
-  </si>
-  <si>
-    <t>East Vinton Road, Westway Number 2 Colonia, TX, 79821</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c12-4532-598e-9540-8d2ff9064c99</t>
-  </si>
-  <si>
-    <t>03/26/2026 12:27:51 PM</t>
-  </si>
-  <si>
-    <t>I 2;US 83, Alamo, TX, 78516</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452b30-2e3b-562e-9623-00fd5f5aaa37</t>
-  </si>
-  <si>
-    <t>03/25/2026 1:58:02 PM</t>
-  </si>
-  <si>
-    <t>7056 Houston</t>
-  </si>
-  <si>
-    <t>12308 Fuqua Street, Houston, TX, 77034</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445265c-62f0-5a30-9f78-0e965473426d</t>
-  </si>
-  <si>
-    <t>03/25/2026 4:27:58 AM</t>
-  </si>
-  <si>
-    <t>RudyRodriguez</t>
-  </si>
-  <si>
-    <t>Northwest Freeway, Houston, TX, 77092-7005</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452452-79b5-5b86-ab7a-7d2cf1ede108</t>
-  </si>
-  <si>
-    <t>03/24/2026 5:36:25 PM</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544521fd-f93c-5cfc-bf4b-eda4db3200bd</t>
-  </si>
-  <si>
-    <t>03/24/2026 12:18:03 PM</t>
-  </si>
-  <si>
-    <t>Southwest Freeway Frontage Road, Houston, TX, 77046</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544520da-7f25-55fe-8055-cbfe201979e7</t>
-  </si>
-  <si>
-    <t>03/23/2026 4:21:48 PM</t>
-  </si>
-  <si>
-    <t>East Loop North, Houston, TX, 77029</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c93-4b3c-5ae0-96d1-31d6e9c7b502</t>
-  </si>
-  <si>
-    <t>03/23/2026 3:18:41 PM</t>
-  </si>
-  <si>
-    <t>8361 Tucson</t>
-  </si>
-  <si>
-    <t>Guy Henderson</t>
-  </si>
-  <si>
-    <t>Nogales, AZ, Tucson, AZ, Yuma, AZ</t>
-  </si>
-  <si>
-    <t>Guy N Henderson - Tucson</t>
-  </si>
-  <si>
-    <t>South Kings Highway, 5.1 mi W Douglas, Cochise County, AZ, 85626</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451c59-81c0-5847-99f6-c62a9f458e43</t>
-  </si>
-  <si>
-    <t>03/23/2026 9:48:17 AM</t>
-  </si>
-  <si>
-    <t>5438 El Paso</t>
-  </si>
-  <si>
-    <t>Northwest Freeway Frontage Road, Jersey Village, TX, 77065:77429</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451b2b-04df-590c-a501-10db316e8507</t>
-  </si>
-  <si>
-    <t>03/22/2026 3:30:41 AM</t>
-  </si>
-  <si>
-    <t>North Loop West, Houston, TX, 77008</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544514aa-f384-571b-bb40-c7e71c4e5e98</t>
-  </si>
-  <si>
-    <t>03/21/2026 3:12:04 PM</t>
-  </si>
-  <si>
-    <t>North Freeway, Houston, TX, 77037</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451206-bb58-5166-ab43-97b58c8dac3d</t>
-  </si>
-  <si>
-    <t>03/20/2026 2:10:51 PM</t>
-  </si>
-  <si>
-    <t>Todd Johnston</t>
-  </si>
-  <si>
-    <t>I 35;US 77, Bellmead, TX, 76705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450ca8-53ba-58de-b474-e36e7dfe067f</t>
-  </si>
-  <si>
-    <t>03/20/2026 11:11:41 AM</t>
-  </si>
-  <si>
-    <t>Moderately Drowsy, Construction, Pedestrians, Light Traffic</t>
-  </si>
-  <si>
-    <t>2755 Clinton Drive, Houston, TX, 77020</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450c04-4b4f-5269-9e3d-ecded278ae39</t>
-  </si>
-  <si>
-    <t>03/20/2026 10:30:12 AM</t>
-  </si>
-  <si>
-    <t>El Cibolo Road, Faysville, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450bde-4fc5-5ad7-b1ad-b3af4a64bdc4</t>
-  </si>
-  <si>
-    <t>03/20/2026 7:11:29 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Raining</t>
-  </si>
-  <si>
-    <t>4957 Hull Street, Houston, TX, 77021</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/28125/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b28-624c-5700-8145-29c59b89af40</t>
   </si>
 </sst>
 </file>
@@ -2194,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2246,119 +2384,119 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>544</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>545</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>546</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>547</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>548</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>430</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>399</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>549</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>550</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>551</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>552</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -2367,597 +2505,597 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>554</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>555</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>556</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>557</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>354</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>558</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>537</v>
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>559</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>560</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>539</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>400</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>561</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>562</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>563</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" t="s">
         <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>242</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" t="s">
-        <v>564</v>
-      </c>
-      <c r="K7" t="s">
-        <v>281</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>566</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>567</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>568</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>569</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>570</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>571</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>572</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>467</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>543</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>573</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s">
-        <v>574</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>575</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>577</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="O10" t="s">
-        <v>579</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>580</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>581</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s">
-        <v>542</v>
+        <v>89</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>582</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>583</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>584</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>585</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>586</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>587</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>588</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
-        <v>319</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>589</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>590</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>591</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>592</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>593</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>594</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>454</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>455</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>595</v>
+        <v>112</v>
       </c>
       <c r="K15" t="s">
-        <v>401</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>596</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>597</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>397</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>398</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" t="s">
-        <v>598</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
-        <v>599</v>
-      </c>
-      <c r="K16" t="s">
-        <v>541</v>
-      </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>600</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -2966,2254 +3104,2254 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
+        <v>127</v>
+      </c>
+      <c r="K18" t="s">
         <v>31</v>
       </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
-        <v>35</v>
-      </c>
-      <c r="K18" t="s">
-        <v>36</v>
-      </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="K19" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="O19" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="K20" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="K21" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>63</v>
+        <v>157</v>
       </c>
       <c r="K22" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="K23" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="K24" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="K25" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>86</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="K26" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H27" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="K27" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="K28" t="s">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="K29" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="K30" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>204</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="K31" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>118</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H32" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="K32" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>128</v>
+        <v>216</v>
       </c>
       <c r="K33" t="s">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>220</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="K34" t="s">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="H35" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="K35" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="K36" t="s">
-        <v>147</v>
+        <v>50</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="F37" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="K37" t="s">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>156</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H38" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="K38" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" t="s">
         <v>29</v>
       </c>
-      <c r="D39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
-      </c>
       <c r="H39" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="K39" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" t="s">
         <v>167</v>
       </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G40" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="K40" t="s">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M40" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>171</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>254</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H41" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="K41" t="s">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="F42" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="G42" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="H42" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="K42" t="s">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="K43" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>191</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>269</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="G44" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="K44" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="C45" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G45" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="K45" t="s">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>201</v>
+        <v>276</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>277</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G46" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H46" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>204</v>
+        <v>278</v>
       </c>
       <c r="K46" t="s">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>207</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="D47" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G47" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="H47" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="K47" t="s">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="O47" t="s">
-        <v>213</v>
+        <v>284</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="C48" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K48" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O48" t="s">
-        <v>219</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="B49" t="s">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="C49" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="K49" t="s">
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N49" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O49" t="s">
-        <v>222</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H50" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I50" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>297</v>
       </c>
       <c r="K50" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N50" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>299</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J51" t="s">
-        <v>229</v>
+        <v>300</v>
       </c>
       <c r="K51" t="s">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="L51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c r="O51" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B52" t="s">
         <v>231</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>232</v>
       </c>
-      <c r="C52" t="s">
-        <v>233</v>
-      </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>305</v>
       </c>
       <c r="H52" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="K52" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>236</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>238</v>
+        <v>155</v>
       </c>
       <c r="G53" t="s">
-        <v>42</v>
+        <v>309</v>
       </c>
       <c r="H53" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="K53" t="s">
-        <v>85</v>
+        <v>311</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="G54" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H54" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="K54" t="s">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>317</v>
       </c>
       <c r="O54" t="s">
-        <v>244</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s">
-        <v>246</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>247</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="H55" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="K55" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N55" t="s">
-        <v>250</v>
+        <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>251</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>252</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="H56" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="K56" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H57" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>327</v>
       </c>
       <c r="J57" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="K57" t="s">
-        <v>147</v>
+        <v>329</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M57" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>330</v>
       </c>
       <c r="O57" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>260</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>333</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>334</v>
       </c>
       <c r="D58" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>336</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>337</v>
       </c>
       <c r="H58" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>261</v>
+        <v>338</v>
       </c>
       <c r="K58" t="s">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>262</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>263</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C59" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D59" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="G59" t="s">
-        <v>264</v>
+        <v>342</v>
       </c>
       <c r="H59" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J59" t="s">
-        <v>265</v>
+        <v>343</v>
       </c>
       <c r="K59" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N59" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>236</v>
       </c>
       <c r="C60" t="s">
-        <v>89</v>
+        <v>237</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I60" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="K60" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D61" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H61" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J61" t="s">
-        <v>273</v>
+        <v>58</v>
       </c>
       <c r="K61" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>276</v>
+        <v>352</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>353</v>
       </c>
       <c r="H62" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>277</v>
+        <v>354</v>
       </c>
       <c r="K62" t="s">
-        <v>122</v>
+        <v>355</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N62" t="s">
-        <v>23</v>
+        <v>356</v>
       </c>
       <c r="O62" t="s">
-        <v>278</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>279</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="D63" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="G63" t="s">
-        <v>42</v>
+        <v>359</v>
       </c>
       <c r="H63" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J63" t="s">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="K63" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M63" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>23</v>
+        <v>362</v>
       </c>
       <c r="O63" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>283</v>
+        <v>364</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>365</v>
       </c>
       <c r="C64" t="s">
+        <v>366</v>
+      </c>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" t="s">
+        <v>270</v>
+      </c>
+      <c r="G64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64" t="s">
         <v>48</v>
       </c>
-      <c r="D64" t="s">
-        <v>49</v>
-      </c>
-      <c r="E64" t="s">
-        <v>50</v>
-      </c>
-      <c r="F64" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" t="s">
-        <v>22</v>
-      </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J64" t="s">
-        <v>284</v>
+        <v>367</v>
       </c>
       <c r="K64" t="s">
-        <v>36</v>
+        <v>368</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M64" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N64" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>285</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>370</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>366</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -5222,1220 +5360,1220 @@
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H65" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J65" t="s">
-        <v>199</v>
+        <v>371</v>
       </c>
       <c r="K65" t="s">
-        <v>287</v>
+        <v>174</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M65" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N65" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>288</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>289</v>
+        <v>373</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>374</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G66" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="H66" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J66" t="s">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="K66" t="s">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N66" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>292</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>293</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H67" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>294</v>
+        <v>378</v>
       </c>
       <c r="K67" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>295</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s">
-        <v>246</v>
+        <v>381</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>382</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>31</v>
+        <v>383</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G68" t="s">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="H68" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>298</v>
+        <v>384</v>
       </c>
       <c r="K68" t="s">
-        <v>299</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>300</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>301</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>323</v>
       </c>
       <c r="D69" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="G69" t="s">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>302</v>
+        <v>387</v>
       </c>
       <c r="K69" t="s">
-        <v>303</v>
+        <v>60</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>304</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>305</v>
+        <v>389</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>381</v>
       </c>
       <c r="C70" t="s">
-        <v>233</v>
+        <v>382</v>
       </c>
       <c r="D70" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>234</v>
+        <v>383</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G70" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J70" t="s">
-        <v>306</v>
+        <v>390</v>
       </c>
       <c r="K70" t="s">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>307</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>308</v>
+        <v>392</v>
       </c>
       <c r="B71" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="H71" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="s">
-        <v>310</v>
+        <v>394</v>
       </c>
       <c r="K71" t="s">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N71" t="s">
-        <v>23</v>
+        <v>395</v>
       </c>
       <c r="O71" t="s">
-        <v>311</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>312</v>
+        <v>397</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>398</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>399</v>
       </c>
       <c r="D72" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="G72" t="s">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="H72" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
       <c r="K72" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="L72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N72" t="s">
-        <v>314</v>
+        <v>26</v>
       </c>
       <c r="O72" t="s">
-        <v>315</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>316</v>
+        <v>401</v>
       </c>
       <c r="B73" t="s">
-        <v>317</v>
+        <v>188</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G73" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="s">
-        <v>318</v>
+        <v>402</v>
       </c>
       <c r="K73" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="L73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M73" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O73" t="s">
-        <v>320</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="B74" t="s">
-        <v>322</v>
+        <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>324</v>
+        <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="H74" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J74" t="s">
-        <v>326</v>
+        <v>405</v>
       </c>
       <c r="K74" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M74" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N74" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O74" t="s">
-        <v>327</v>
+        <v>406</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>328</v>
+        <v>407</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C75" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G75" t="s">
-        <v>329</v>
+        <v>408</v>
       </c>
       <c r="H75" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
-        <v>112</v>
+        <v>409</v>
       </c>
       <c r="K75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N75" t="s">
-        <v>23</v>
+        <v>356</v>
       </c>
       <c r="O75" t="s">
-        <v>330</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>331</v>
+        <v>411</v>
       </c>
       <c r="B76" t="s">
-        <v>317</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E76" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F76" t="s">
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H76" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I76" t="s">
-        <v>23</v>
+        <v>412</v>
       </c>
       <c r="J76" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="K76" t="s">
-        <v>122</v>
+        <v>414</v>
       </c>
       <c r="L76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>333</v>
+        <v>415</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>334</v>
+        <v>416</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>269</v>
       </c>
       <c r="C77" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G77" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H77" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J77" t="s">
-        <v>290</v>
+        <v>417</v>
       </c>
       <c r="K77" t="s">
-        <v>92</v>
+        <v>418</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>335</v>
+        <v>419</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>336</v>
+        <v>420</v>
       </c>
       <c r="B78" t="s">
-        <v>253</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F78" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="G78" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="H78" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J78" t="s">
-        <v>112</v>
+        <v>421</v>
       </c>
       <c r="K78" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N78" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>338</v>
+        <v>422</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>339</v>
+        <v>423</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H79" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J79" t="s">
-        <v>340</v>
+        <v>424</v>
       </c>
       <c r="K79" t="s">
-        <v>341</v>
+        <v>89</v>
       </c>
       <c r="L79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M79" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>342</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="C80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D80" t="s">
         <v>132</v>
       </c>
-      <c r="D80" t="s">
-        <v>30</v>
-      </c>
       <c r="E80" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J80" t="s">
-        <v>344</v>
+        <v>427</v>
       </c>
       <c r="K80" t="s">
-        <v>345</v>
+        <v>228</v>
       </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M80" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H81" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J81" t="s">
-        <v>348</v>
+        <v>58</v>
       </c>
       <c r="K81" t="s">
-        <v>349</v>
+        <v>430</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M81" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="B82" t="s">
-        <v>352</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="D82" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="G82" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H82" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J82" t="s">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="K82" t="s">
-        <v>194</v>
+        <v>434</v>
       </c>
       <c r="L82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>356</v>
+        <v>435</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>357</v>
+        <v>436</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>290</v>
       </c>
       <c r="C83" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>67</v>
+      </c>
+      <c r="G83" t="s">
         <v>29</v>
       </c>
-      <c r="D83" t="s">
-        <v>30</v>
-      </c>
-      <c r="E83" t="s">
-        <v>31</v>
-      </c>
-      <c r="F83" t="s">
-        <v>32</v>
-      </c>
-      <c r="G83" t="s">
-        <v>33</v>
-      </c>
       <c r="H83" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J83" t="s">
-        <v>358</v>
+        <v>437</v>
       </c>
       <c r="K83" t="s">
-        <v>103</v>
+        <v>329</v>
       </c>
       <c r="L83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O83" t="s">
-        <v>359</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>360</v>
+        <v>439</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>440</v>
       </c>
       <c r="H84" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J84" t="s">
-        <v>361</v>
+        <v>441</v>
       </c>
       <c r="K84" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="L84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N84" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>363</v>
+        <v>443</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="D85" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H85" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J85" t="s">
-        <v>364</v>
+        <v>444</v>
       </c>
       <c r="K85" t="s">
-        <v>365</v>
+        <v>445</v>
       </c>
       <c r="L85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>366</v>
+        <v>446</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>367</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C86" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>31</v>
+        <v>383</v>
       </c>
       <c r="F86" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" t="s">
-        <v>370</v>
+        <v>448</v>
       </c>
       <c r="K86" t="s">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N86" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>371</v>
+        <v>449</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>372</v>
+        <v>450</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
-        <v>373</v>
+        <v>242</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="H87" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>374</v>
+        <v>452</v>
       </c>
       <c r="K87" t="s">
-        <v>185</v>
+        <v>283</v>
       </c>
       <c r="L87" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M87" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N87" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>375</v>
+        <v>453</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>376</v>
+        <v>454</v>
       </c>
       <c r="B88" t="s">
-        <v>377</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>378</v>
+        <v>189</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G88" t="s">
-        <v>33</v>
+        <v>455</v>
       </c>
       <c r="H88" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I88" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J88" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="K88" t="s">
-        <v>103</v>
+        <v>244</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M88" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N88" t="s">
-        <v>23</v>
+        <v>456</v>
       </c>
       <c r="O88" t="s">
-        <v>380</v>
+        <v>457</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>381</v>
+        <v>458</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>459</v>
       </c>
       <c r="C89" t="s">
-        <v>378</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E89" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F89" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G89" t="s">
         <v>21</v>
       </c>
       <c r="H89" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I89" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J89" t="s">
-        <v>382</v>
+        <v>460</v>
       </c>
       <c r="K89" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="L89" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M89" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N89" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="O89" t="s">
-        <v>383</v>
+        <v>461</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>384</v>
+        <v>462</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>463</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>464</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>465</v>
       </c>
       <c r="E90" t="s">
-        <v>31</v>
+        <v>466</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="G90" t="s">
-        <v>33</v>
+        <v>359</v>
       </c>
       <c r="H90" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J90" t="s">
-        <v>385</v>
+        <v>467</v>
       </c>
       <c r="K90" t="s">
-        <v>281</v>
+        <v>36</v>
       </c>
       <c r="L90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O90" t="s">
-        <v>386</v>
+        <v>468</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="C91" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -6444,1408 +6582,1408 @@
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G91" t="s">
-        <v>42</v>
+        <v>470</v>
       </c>
       <c r="H91" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I91" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J91" t="s">
-        <v>388</v>
+        <v>282</v>
       </c>
       <c r="K91" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="L91" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M91" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N91" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O91" t="s">
-        <v>389</v>
+        <v>471</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>390</v>
+        <v>472</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>459</v>
       </c>
       <c r="C92" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E92" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F92" t="s">
-        <v>238</v>
+        <v>67</v>
       </c>
       <c r="G92" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J92" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="K92" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="L92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N92" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>393</v>
+        <v>475</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="C93" t="s">
-        <v>168</v>
+        <v>323</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H93" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J93" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="K93" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="L93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N93" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O93" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="B94" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C94" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G94" t="s">
-        <v>399</v>
+        <v>478</v>
       </c>
       <c r="H94" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J94" t="s">
-        <v>400</v>
+        <v>282</v>
       </c>
       <c r="K94" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="L94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N94" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O94" t="s">
-        <v>402</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>403</v>
+        <v>480</v>
       </c>
       <c r="B95" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D95" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="G95" t="s">
-        <v>404</v>
+        <v>29</v>
       </c>
       <c r="H95" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J95" t="s">
-        <v>405</v>
+        <v>481</v>
       </c>
       <c r="K95" t="s">
-        <v>113</v>
+        <v>482</v>
       </c>
       <c r="L95" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M95" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N95" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O95" t="s">
-        <v>406</v>
+        <v>483</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>407</v>
+        <v>484</v>
       </c>
       <c r="B96" t="s">
-        <v>408</v>
+        <v>171</v>
       </c>
       <c r="C96" t="s">
-        <v>409</v>
+        <v>172</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G96" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="H96" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J96" t="s">
-        <v>410</v>
+        <v>485</v>
       </c>
       <c r="K96" t="s">
-        <v>122</v>
+        <v>486</v>
       </c>
       <c r="L96" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M96" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="N96" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O96" t="s">
-        <v>411</v>
+        <v>487</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>412</v>
+        <v>488</v>
       </c>
       <c r="B97" t="s">
-        <v>413</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>414</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E97" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="F97" t="s">
         <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H97" t="s">
         <v>22</v>
       </c>
       <c r="I97" t="s">
-        <v>415</v>
+        <v>26</v>
       </c>
       <c r="J97" t="s">
-        <v>255</v>
+        <v>489</v>
       </c>
       <c r="K97" t="s">
-        <v>416</v>
+        <v>490</v>
       </c>
       <c r="L97" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M97" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N97" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O97" t="s">
-        <v>417</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>418</v>
+        <v>492</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>493</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>494</v>
       </c>
       <c r="D98" t="s">
-        <v>23</v>
+        <v>335</v>
       </c>
       <c r="E98" t="s">
-        <v>153</v>
+        <v>336</v>
       </c>
       <c r="F98" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="H98" t="s">
         <v>22</v>
       </c>
       <c r="I98" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J98" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="K98" t="s">
-        <v>36</v>
+        <v>347</v>
       </c>
       <c r="L98" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M98" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N98" t="s">
-        <v>420</v>
+        <v>26</v>
       </c>
       <c r="O98" t="s">
-        <v>421</v>
+        <v>496</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>422</v>
+        <v>497</v>
       </c>
       <c r="B99" t="s">
-        <v>423</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>424</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>425</v>
+        <v>29</v>
       </c>
       <c r="H99" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I99" t="s">
-        <v>415</v>
+        <v>26</v>
       </c>
       <c r="J99" t="s">
-        <v>426</v>
+        <v>498</v>
       </c>
       <c r="K99" t="s">
-        <v>427</v>
+        <v>36</v>
       </c>
       <c r="L99" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M99" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N99" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O99" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
       <c r="B100" t="s">
-        <v>430</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>431</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H100" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J100" t="s">
-        <v>433</v>
+        <v>501</v>
       </c>
       <c r="K100" t="s">
-        <v>44</v>
+        <v>292</v>
       </c>
       <c r="L100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O100" t="s">
-        <v>434</v>
+        <v>502</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>435</v>
+        <v>503</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C101" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D101" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E101" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F101" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G101" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H101" t="s">
         <v>22</v>
       </c>
       <c r="I101" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J101" t="s">
-        <v>436</v>
+        <v>504</v>
       </c>
       <c r="K101" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="L101" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M101" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N101" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O101" t="s">
-        <v>437</v>
+        <v>505</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>438</v>
+        <v>506</v>
       </c>
       <c r="B102" t="s">
-        <v>95</v>
+        <v>507</v>
       </c>
       <c r="C102" t="s">
-        <v>62</v>
+        <v>508</v>
       </c>
       <c r="D102" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="G102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J102" t="s">
-        <v>306</v>
+        <v>509</v>
       </c>
       <c r="K102" t="s">
-        <v>274</v>
+        <v>486</v>
       </c>
       <c r="L102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O102" t="s">
-        <v>439</v>
+        <v>510</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>440</v>
+        <v>511</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C103" t="s">
-        <v>441</v>
+        <v>512</v>
       </c>
       <c r="D103" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="G103" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H103" t="s">
         <v>22</v>
       </c>
       <c r="I103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J103" t="s">
-        <v>443</v>
+        <v>513</v>
       </c>
       <c r="K103" t="s">
-        <v>444</v>
+        <v>339</v>
       </c>
       <c r="L103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M103" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N103" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="O103" t="s">
-        <v>445</v>
+        <v>514</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="B104" t="s">
-        <v>39</v>
+        <v>516</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>517</v>
       </c>
       <c r="D104" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G104" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="H104" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I104" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J104" t="s">
-        <v>447</v>
+        <v>518</v>
       </c>
       <c r="K104" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L104" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M104" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N104" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O104" t="s">
-        <v>448</v>
+        <v>519</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>449</v>
+        <v>520</v>
       </c>
       <c r="B105" t="s">
-        <v>55</v>
+        <v>516</v>
       </c>
       <c r="C105" t="s">
-        <v>62</v>
+        <v>517</v>
       </c>
       <c r="D105" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H105" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I105" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J105" t="s">
-        <v>450</v>
+        <v>521</v>
       </c>
       <c r="K105" t="s">
-        <v>451</v>
+        <v>206</v>
       </c>
       <c r="L105" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M105" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N105" t="s">
-        <v>23</v>
+        <v>256</v>
       </c>
       <c r="O105" t="s">
-        <v>452</v>
+        <v>522</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>453</v>
+        <v>523</v>
       </c>
       <c r="B106" t="s">
-        <v>454</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>455</v>
+        <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="E106" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
       </c>
       <c r="G106" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H106" t="s">
         <v>22</v>
       </c>
       <c r="I106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J106" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="K106" t="s">
-        <v>416</v>
+        <v>89</v>
       </c>
       <c r="L106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N106" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O106" t="s">
-        <v>457</v>
+        <v>525</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>458</v>
+        <v>526</v>
       </c>
       <c r="B107" t="s">
-        <v>377</v>
+        <v>53</v>
       </c>
       <c r="C107" t="s">
-        <v>378</v>
+        <v>54</v>
       </c>
       <c r="D107" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E107" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F107" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H107" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I107" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J107" t="s">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="L107" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M107" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N107" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O107" t="s">
-        <v>460</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="B108" t="s">
-        <v>377</v>
+        <v>153</v>
       </c>
       <c r="C108" t="s">
-        <v>378</v>
+        <v>323</v>
       </c>
       <c r="D108" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="G108" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H108" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J108" t="s">
-        <v>391</v>
+        <v>530</v>
       </c>
       <c r="K108" t="s">
-        <v>345</v>
+        <v>482</v>
       </c>
       <c r="L108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N108" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O108" t="s">
-        <v>462</v>
+        <v>531</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="B109" t="s">
-        <v>464</v>
+        <v>153</v>
       </c>
       <c r="C109" t="s">
-        <v>465</v>
+        <v>323</v>
       </c>
       <c r="D109" t="s">
-        <v>466</v>
+        <v>18</v>
       </c>
       <c r="E109" t="s">
-        <v>467</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H109" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I109" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J109" t="s">
-        <v>468</v>
+        <v>533</v>
       </c>
       <c r="K109" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="L109" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M109" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N109" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O109" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>470</v>
+        <v>535</v>
       </c>
       <c r="B110" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="C110" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="D110" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G110" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="H110" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J110" t="s">
-        <v>471</v>
+        <v>163</v>
       </c>
       <c r="K110" t="s">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O110" t="s">
-        <v>472</v>
+        <v>536</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>473</v>
+        <v>537</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>333</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>334</v>
       </c>
       <c r="D111" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="E111" t="s">
-        <v>31</v>
+        <v>336</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="G111" t="s">
-        <v>33</v>
+        <v>538</v>
       </c>
       <c r="H111" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J111" t="s">
-        <v>474</v>
+        <v>539</v>
       </c>
       <c r="K111" t="s">
-        <v>475</v>
+        <v>283</v>
       </c>
       <c r="L111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O111" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>477</v>
+        <v>541</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>542</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>543</v>
       </c>
       <c r="D112" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G112" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H112" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I112" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J112" t="s">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="K112" t="s">
-        <v>479</v>
+        <v>292</v>
       </c>
       <c r="L112" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M112" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N112" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O112" t="s">
-        <v>480</v>
+        <v>545</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>481</v>
+        <v>546</v>
       </c>
       <c r="B113" t="s">
-        <v>95</v>
+        <v>547</v>
       </c>
       <c r="C113" t="s">
-        <v>96</v>
+        <v>548</v>
       </c>
       <c r="D113" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E113" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G113" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H113" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I113" t="s">
         <v>23</v>
       </c>
       <c r="J113" t="s">
-        <v>482</v>
+        <v>39</v>
       </c>
       <c r="K113" t="s">
-        <v>226</v>
+        <v>549</v>
       </c>
       <c r="L113" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M113" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N113" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O113" t="s">
-        <v>483</v>
+        <v>550</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>484</v>
+        <v>551</v>
       </c>
       <c r="B114" t="s">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="C114" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="D114" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E114" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="G114" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H114" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I114" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J114" t="s">
-        <v>485</v>
+        <v>552</v>
       </c>
       <c r="K114" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="L114" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M114" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N114" t="s">
-        <v>23</v>
+        <v>553</v>
       </c>
       <c r="O114" t="s">
-        <v>486</v>
+        <v>554</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>487</v>
+        <v>555</v>
       </c>
       <c r="B115" t="s">
-        <v>397</v>
+        <v>556</v>
       </c>
       <c r="C115" t="s">
-        <v>398</v>
+        <v>557</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E115" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="G115" t="s">
-        <v>42</v>
+        <v>558</v>
       </c>
       <c r="H115" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I115" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="J115" t="s">
-        <v>306</v>
+        <v>559</v>
       </c>
       <c r="K115" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L115" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M115" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N115" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O115" t="s">
-        <v>489</v>
+        <v>560</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>490</v>
+        <v>561</v>
       </c>
       <c r="B116" t="s">
-        <v>397</v>
+        <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>398</v>
+        <v>140</v>
       </c>
       <c r="D116" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="E116" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="F116" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="G116" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H116" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I116" t="s">
-        <v>488</v>
+        <v>26</v>
       </c>
       <c r="J116" t="s">
-        <v>400</v>
+        <v>562</v>
       </c>
       <c r="K116" t="s">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="L116" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M116" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O116" t="s">
-        <v>491</v>
+        <v>563</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>492</v>
+        <v>564</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="C117" t="s">
+        <v>260</v>
+      </c>
+      <c r="D117" t="s">
+        <v>141</v>
+      </c>
+      <c r="E117" t="s">
+        <v>66</v>
+      </c>
+      <c r="F117" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117" t="s">
         <v>29</v>
       </c>
-      <c r="D117" t="s">
-        <v>30</v>
-      </c>
-      <c r="E117" t="s">
-        <v>31</v>
-      </c>
-      <c r="F117" t="s">
-        <v>32</v>
-      </c>
-      <c r="G117" t="s">
-        <v>33</v>
-      </c>
       <c r="H117" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I117" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J117" t="s">
-        <v>493</v>
+        <v>565</v>
       </c>
       <c r="K117" t="s">
-        <v>416</v>
+        <v>301</v>
       </c>
       <c r="L117" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M117" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N117" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O117" t="s">
-        <v>494</v>
+        <v>566</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>495</v>
+        <v>567</v>
       </c>
       <c r="B118" t="s">
-        <v>423</v>
+        <v>269</v>
       </c>
       <c r="C118" t="s">
-        <v>424</v>
+        <v>195</v>
       </c>
       <c r="D118" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E118" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="G118" t="s">
-        <v>496</v>
+        <v>29</v>
       </c>
       <c r="H118" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I118" t="s">
-        <v>415</v>
+        <v>26</v>
       </c>
       <c r="J118" t="s">
-        <v>497</v>
+        <v>448</v>
       </c>
       <c r="K118" t="s">
-        <v>274</v>
+        <v>418</v>
       </c>
       <c r="L118" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M118" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N118" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O118" t="s">
-        <v>498</v>
+        <v>568</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>499</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>570</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E119" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F119" t="s">
-        <v>32</v>
+        <v>571</v>
       </c>
       <c r="G119" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H119" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I119" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J119" t="s">
-        <v>501</v>
+        <v>84</v>
       </c>
       <c r="K119" t="s">
-        <v>64</v>
+        <v>572</v>
       </c>
       <c r="L119" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M119" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N119" t="s">
-        <v>23</v>
+        <v>356</v>
       </c>
       <c r="O119" t="s">
-        <v>502</v>
+        <v>573</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>503</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="C120" t="s">
-        <v>323</v>
+        <v>232</v>
       </c>
       <c r="D120" t="s">
-        <v>324</v>
+        <v>18</v>
       </c>
       <c r="E120" t="s">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G120" t="s">
-        <v>33</v>
+        <v>342</v>
       </c>
       <c r="H120" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I120" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J120" t="s">
-        <v>504</v>
+        <v>575</v>
       </c>
       <c r="K120" t="s">
-        <v>505</v>
+        <v>25</v>
       </c>
       <c r="L120" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M120" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N120" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O120" t="s">
-        <v>506</v>
+        <v>576</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>507</v>
+        <v>577</v>
       </c>
       <c r="B121" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
@@ -7854,316 +7992,927 @@
         <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G121" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H121" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I121" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J121" t="s">
-        <v>508</v>
+        <v>578</v>
       </c>
       <c r="K121" t="s">
-        <v>509</v>
+        <v>579</v>
       </c>
       <c r="L121" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M121" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N121" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O121" t="s">
-        <v>510</v>
+        <v>580</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>511</v>
+        <v>581</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="C122" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D122" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E122" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="G122" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="H122" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J122" t="s">
-        <v>512</v>
+        <v>582</v>
       </c>
       <c r="K122" t="s">
-        <v>64</v>
+        <v>549</v>
       </c>
       <c r="L122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N122" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O122" t="s">
-        <v>513</v>
+        <v>583</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>514</v>
+        <v>584</v>
       </c>
       <c r="B123" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C123" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D123" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="G123" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="H123" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I123" t="s">
-        <v>517</v>
+        <v>26</v>
       </c>
       <c r="J123" t="s">
-        <v>518</v>
+        <v>585</v>
       </c>
       <c r="K123" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L123" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M123" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N123" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O123" t="s">
-        <v>519</v>
+        <v>586</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>520</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>516</v>
       </c>
       <c r="C124" t="s">
-        <v>247</v>
+        <v>517</v>
       </c>
       <c r="D124" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s">
-        <v>521</v>
+        <v>34</v>
       </c>
       <c r="H124" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I124" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J124" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="K124" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="L124" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M124" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="N124" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O124" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>525</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s">
-        <v>377</v>
+        <v>590</v>
       </c>
       <c r="C125" t="s">
-        <v>378</v>
+        <v>591</v>
       </c>
       <c r="D125" t="s">
-        <v>30</v>
+        <v>592</v>
       </c>
       <c r="E125" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F125" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="G125" t="s">
-        <v>526</v>
+        <v>29</v>
       </c>
       <c r="H125" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I125" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J125" t="s">
-        <v>527</v>
+        <v>593</v>
       </c>
       <c r="K125" t="s">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="L125" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M125" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N125" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O125" t="s">
-        <v>528</v>
+        <v>594</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>529</v>
+        <v>595</v>
       </c>
       <c r="B126" t="s">
-        <v>413</v>
+        <v>269</v>
       </c>
       <c r="C126" t="s">
+        <v>195</v>
+      </c>
+      <c r="D126" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" t="s">
+        <v>67</v>
+      </c>
+      <c r="G126" t="s">
         <v>29</v>
       </c>
-      <c r="D126" t="s">
-        <v>30</v>
-      </c>
-      <c r="E126" t="s">
-        <v>31</v>
-      </c>
-      <c r="F126" t="s">
-        <v>20</v>
-      </c>
-      <c r="G126" t="s">
-        <v>530</v>
-      </c>
       <c r="H126" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I126" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J126" t="s">
-        <v>531</v>
+        <v>596</v>
       </c>
       <c r="K126" t="s">
-        <v>532</v>
+        <v>248</v>
       </c>
       <c r="L126" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M126" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N126" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O126" t="s">
-        <v>533</v>
+        <v>597</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>534</v>
+        <v>598</v>
       </c>
       <c r="B127" t="s">
-        <v>215</v>
+        <v>16</v>
       </c>
       <c r="C127" t="s">
-        <v>216</v>
+        <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E127" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="G127" t="s">
-        <v>535</v>
+        <v>29</v>
       </c>
       <c r="H127" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" t="s">
+        <v>26</v>
+      </c>
+      <c r="J127" t="s">
+        <v>599</v>
+      </c>
+      <c r="K127" t="s">
+        <v>600</v>
+      </c>
+      <c r="L127" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" t="s">
+        <v>26</v>
+      </c>
+      <c r="N127" t="s">
+        <v>26</v>
+      </c>
+      <c r="O127" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>602</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" t="s">
         <v>34</v>
       </c>
-      <c r="I127" t="s">
-        <v>488</v>
-      </c>
-      <c r="J127" t="s">
-        <v>536</v>
-      </c>
-      <c r="K127" t="s">
-        <v>537</v>
-      </c>
-      <c r="L127" t="s">
+      <c r="H128" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" t="s">
+        <v>26</v>
+      </c>
+      <c r="J128" t="s">
+        <v>603</v>
+      </c>
+      <c r="K128" t="s">
+        <v>109</v>
+      </c>
+      <c r="L128" t="s">
+        <v>26</v>
+      </c>
+      <c r="M128" t="s">
+        <v>26</v>
+      </c>
+      <c r="N128" t="s">
+        <v>26</v>
+      </c>
+      <c r="O128" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>605</v>
+      </c>
+      <c r="B129" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" t="s">
+        <v>101</v>
+      </c>
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" t="s">
+        <v>67</v>
+      </c>
+      <c r="G129" t="s">
+        <v>34</v>
+      </c>
+      <c r="H129" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" t="s">
+        <v>606</v>
+      </c>
+      <c r="K129" t="s">
+        <v>181</v>
+      </c>
+      <c r="L129" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" t="s">
+        <v>26</v>
+      </c>
+      <c r="N129" t="s">
+        <v>26</v>
+      </c>
+      <c r="O129" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>608</v>
+      </c>
+      <c r="B130" t="s">
+        <v>547</v>
+      </c>
+      <c r="C130" t="s">
+        <v>323</v>
+      </c>
+      <c r="D130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" t="s">
+        <v>67</v>
+      </c>
+      <c r="G130" t="s">
+        <v>29</v>
+      </c>
+      <c r="H130" t="s">
+        <v>22</v>
+      </c>
+      <c r="I130" t="s">
+        <v>26</v>
+      </c>
+      <c r="J130" t="s">
+        <v>609</v>
+      </c>
+      <c r="K130" t="s">
+        <v>287</v>
+      </c>
+      <c r="L130" t="s">
+        <v>26</v>
+      </c>
+      <c r="M130" t="s">
+        <v>26</v>
+      </c>
+      <c r="N130" t="s">
+        <v>26</v>
+      </c>
+      <c r="O130" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>611</v>
+      </c>
+      <c r="B131" t="s">
+        <v>213</v>
+      </c>
+      <c r="C131" t="s">
+        <v>214</v>
+      </c>
+      <c r="D131" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" t="s">
+        <v>19</v>
+      </c>
+      <c r="F131" t="s">
+        <v>57</v>
+      </c>
+      <c r="G131" t="s">
+        <v>34</v>
+      </c>
+      <c r="H131" t="s">
+        <v>22</v>
+      </c>
+      <c r="I131" t="s">
+        <v>612</v>
+      </c>
+      <c r="J131" t="s">
+        <v>448</v>
+      </c>
+      <c r="K131" t="s">
+        <v>283</v>
+      </c>
+      <c r="L131" t="s">
+        <v>26</v>
+      </c>
+      <c r="M131" t="s">
+        <v>60</v>
+      </c>
+      <c r="N131" t="s">
+        <v>26</v>
+      </c>
+      <c r="O131" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>614</v>
+      </c>
+      <c r="B132" t="s">
+        <v>213</v>
+      </c>
+      <c r="C132" t="s">
+        <v>214</v>
+      </c>
+      <c r="D132" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" t="s">
+        <v>19</v>
+      </c>
+      <c r="F132" t="s">
+        <v>47</v>
+      </c>
+      <c r="G132" t="s">
+        <v>21</v>
+      </c>
+      <c r="H132" t="s">
+        <v>22</v>
+      </c>
+      <c r="I132" t="s">
+        <v>612</v>
+      </c>
+      <c r="J132" t="s">
+        <v>163</v>
+      </c>
+      <c r="K132" t="s">
+        <v>490</v>
+      </c>
+      <c r="L132" t="s">
+        <v>26</v>
+      </c>
+      <c r="M132" t="s">
+        <v>26</v>
+      </c>
+      <c r="N132" t="s">
+        <v>26</v>
+      </c>
+      <c r="O132" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>616</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" t="s">
+        <v>19</v>
+      </c>
+      <c r="F133" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" t="s">
+        <v>29</v>
+      </c>
+      <c r="H133" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J133" t="s">
+        <v>617</v>
+      </c>
+      <c r="K133" t="s">
+        <v>549</v>
+      </c>
+      <c r="L133" t="s">
+        <v>26</v>
+      </c>
+      <c r="M133" t="s">
+        <v>26</v>
+      </c>
+      <c r="N133" t="s">
+        <v>26</v>
+      </c>
+      <c r="O133" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>619</v>
+      </c>
+      <c r="B134" t="s">
+        <v>556</v>
+      </c>
+      <c r="C134" t="s">
+        <v>557</v>
+      </c>
+      <c r="D134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" t="s">
+        <v>19</v>
+      </c>
+      <c r="F134" t="s">
+        <v>155</v>
+      </c>
+      <c r="G134" t="s">
+        <v>620</v>
+      </c>
+      <c r="H134" t="s">
+        <v>22</v>
+      </c>
+      <c r="I134" t="s">
         <v>23</v>
       </c>
-      <c r="M127" t="s">
-        <v>23</v>
-      </c>
-      <c r="N127" t="s">
-        <v>23</v>
-      </c>
-      <c r="O127" t="s">
-        <v>538</v>
+      <c r="J134" t="s">
+        <v>621</v>
+      </c>
+      <c r="K134" t="s">
+        <v>418</v>
+      </c>
+      <c r="L134" t="s">
+        <v>26</v>
+      </c>
+      <c r="M134" t="s">
+        <v>26</v>
+      </c>
+      <c r="N134" t="s">
+        <v>26</v>
+      </c>
+      <c r="O134" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>623</v>
+      </c>
+      <c r="B135" t="s">
+        <v>624</v>
+      </c>
+      <c r="C135" t="s">
+        <v>26</v>
+      </c>
+      <c r="D135" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" t="s">
+        <v>29</v>
+      </c>
+      <c r="H135" t="s">
+        <v>48</v>
+      </c>
+      <c r="I135" t="s">
+        <v>26</v>
+      </c>
+      <c r="J135" t="s">
+        <v>625</v>
+      </c>
+      <c r="K135" t="s">
+        <v>248</v>
+      </c>
+      <c r="L135" t="s">
+        <v>26</v>
+      </c>
+      <c r="M135" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" t="s">
+        <v>26</v>
+      </c>
+      <c r="O135" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>627</v>
+      </c>
+      <c r="B136" t="s">
+        <v>463</v>
+      </c>
+      <c r="C136" t="s">
+        <v>464</v>
+      </c>
+      <c r="D136" t="s">
+        <v>465</v>
+      </c>
+      <c r="E136" t="s">
+        <v>466</v>
+      </c>
+      <c r="F136" t="s">
+        <v>67</v>
+      </c>
+      <c r="G136" t="s">
+        <v>29</v>
+      </c>
+      <c r="H136" t="s">
+        <v>22</v>
+      </c>
+      <c r="I136" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" t="s">
+        <v>628</v>
+      </c>
+      <c r="K136" t="s">
+        <v>629</v>
+      </c>
+      <c r="L136" t="s">
+        <v>26</v>
+      </c>
+      <c r="M136" t="s">
+        <v>26</v>
+      </c>
+      <c r="N136" t="s">
+        <v>26</v>
+      </c>
+      <c r="O136" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>631</v>
+      </c>
+      <c r="B137" t="s">
+        <v>53</v>
+      </c>
+      <c r="C137" t="s">
+        <v>54</v>
+      </c>
+      <c r="D137" t="s">
+        <v>55</v>
+      </c>
+      <c r="E137" t="s">
+        <v>56</v>
+      </c>
+      <c r="F137" t="s">
+        <v>94</v>
+      </c>
+      <c r="G137" t="s">
+        <v>34</v>
+      </c>
+      <c r="H137" t="s">
+        <v>22</v>
+      </c>
+      <c r="I137" t="s">
+        <v>26</v>
+      </c>
+      <c r="J137" t="s">
+        <v>632</v>
+      </c>
+      <c r="K137" t="s">
+        <v>633</v>
+      </c>
+      <c r="L137" t="s">
+        <v>26</v>
+      </c>
+      <c r="M137" t="s">
+        <v>26</v>
+      </c>
+      <c r="N137" t="s">
+        <v>26</v>
+      </c>
+      <c r="O137" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>635</v>
+      </c>
+      <c r="B138" t="s">
+        <v>269</v>
+      </c>
+      <c r="C138" t="s">
+        <v>195</v>
+      </c>
+      <c r="D138" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" t="s">
+        <v>67</v>
+      </c>
+      <c r="G138" t="s">
+        <v>21</v>
+      </c>
+      <c r="H138" t="s">
+        <v>22</v>
+      </c>
+      <c r="I138" t="s">
+        <v>26</v>
+      </c>
+      <c r="J138" t="s">
+        <v>636</v>
+      </c>
+      <c r="K138" t="s">
+        <v>248</v>
+      </c>
+      <c r="L138" t="s">
+        <v>26</v>
+      </c>
+      <c r="M138" t="s">
+        <v>26</v>
+      </c>
+      <c r="N138" t="s">
+        <v>26</v>
+      </c>
+      <c r="O138" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>638</v>
+      </c>
+      <c r="B139" t="s">
+        <v>639</v>
+      </c>
+      <c r="C139" t="s">
+        <v>640</v>
+      </c>
+      <c r="D139" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" t="s">
+        <v>67</v>
+      </c>
+      <c r="G139" t="s">
+        <v>29</v>
+      </c>
+      <c r="H139" t="s">
+        <v>22</v>
+      </c>
+      <c r="I139" t="s">
+        <v>327</v>
+      </c>
+      <c r="J139" t="s">
+        <v>641</v>
+      </c>
+      <c r="K139" t="s">
+        <v>486</v>
+      </c>
+      <c r="L139" t="s">
+        <v>26</v>
+      </c>
+      <c r="M139" t="s">
+        <v>26</v>
+      </c>
+      <c r="N139" t="s">
+        <v>26</v>
+      </c>
+      <c r="O139" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>643</v>
+      </c>
+      <c r="B140" t="s">
+        <v>92</v>
+      </c>
+      <c r="C140" t="s">
+        <v>93</v>
+      </c>
+      <c r="D140" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" t="s">
+        <v>57</v>
+      </c>
+      <c r="G140" t="s">
+        <v>95</v>
+      </c>
+      <c r="H140" t="s">
+        <v>22</v>
+      </c>
+      <c r="I140" t="s">
+        <v>26</v>
+      </c>
+      <c r="J140" t="s">
+        <v>644</v>
+      </c>
+      <c r="K140" t="s">
+        <v>645</v>
+      </c>
+      <c r="L140" t="s">
+        <v>26</v>
+      </c>
+      <c r="M140" t="s">
+        <v>60</v>
+      </c>
+      <c r="N140" t="s">
+        <v>26</v>
+      </c>
+      <c r="O140" t="s">
+        <v>646</v>
       </c>
     </row>
   </sheetData>
